--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="34">
   <si>
     <t>日期</t>
   </si>
@@ -91,9 +91,6 @@
   </si>
   <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>0910</t>
   </si>
   <si>
     <t>用户id</t>
@@ -819,7 +816,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -856,7 +853,7 @@
     <xf numFmtId="10" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1384,8 +1381,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S3"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2"/>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5"/>
   <sheetData>
     <row r="1" ht="28" spans="1:19">
       <c r="A1" s="8" t="s">
@@ -1444,7 +1441,7 @@
     </row>
     <row r="2" ht="28" spans="1:19">
       <c r="A2" s="6">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>17</v>
@@ -1453,37 +1450,37 @@
         <v>18</v>
       </c>
       <c r="D2" s="4">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E2" s="4">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F2" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G2" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" s="11">
-        <v>0.2</v>
+        <v>0.1429</v>
       </c>
       <c r="L2" s="11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M2" s="11">
         <v>1</v>
       </c>
       <c r="N2" s="11">
-        <v>0.1</v>
+        <v>0.1429</v>
       </c>
       <c r="O2" s="4">
         <v>0</v>
@@ -1492,14 +1489,14 @@
         <v>0</v>
       </c>
       <c r="Q2" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R2" s="4"/>
       <c r="S2" s="6"/>
     </row>
     <row r="3" customFormat="1" ht="28" spans="1:19">
       <c r="A3" s="6">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>17</v>
@@ -1508,16 +1505,16 @@
         <v>18</v>
       </c>
       <c r="D3" s="4">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E3" s="4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F3" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3" s="4">
         <v>2</v>
@@ -1529,16 +1526,16 @@
         <v>2</v>
       </c>
       <c r="K3" s="11">
-        <v>0.16</v>
+        <v>0.2308</v>
       </c>
       <c r="L3" s="11">
-        <v>0.5</v>
+        <v>0.6667</v>
       </c>
       <c r="M3" s="11">
         <v>1</v>
       </c>
       <c r="N3" s="11">
-        <v>0.08</v>
+        <v>0.1538</v>
       </c>
       <c r="O3" s="4">
         <v>0</v>
@@ -1551,6 +1548,171 @@
       </c>
       <c r="R3" s="4"/>
       <c r="S3" s="6"/>
+    </row>
+    <row r="4" ht="28" spans="1:19">
+      <c r="A4" s="6">
+        <v>908</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="4">
+        <v>20</v>
+      </c>
+      <c r="E4" s="4">
+        <v>9</v>
+      </c>
+      <c r="F4" s="4">
+        <v>4</v>
+      </c>
+      <c r="G4" s="4">
+        <v>3</v>
+      </c>
+      <c r="H4" s="4">
+        <v>2</v>
+      </c>
+      <c r="I4" s="4">
+        <v>2</v>
+      </c>
+      <c r="J4" s="4">
+        <v>2</v>
+      </c>
+      <c r="K4" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="L4" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="M4" s="11">
+        <v>1</v>
+      </c>
+      <c r="N4" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>2</v>
+      </c>
+      <c r="R4" s="4"/>
+      <c r="S4" s="6"/>
+    </row>
+    <row r="5" ht="28" spans="1:19">
+      <c r="A5" s="6">
+        <v>909</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4">
+        <v>9</v>
+      </c>
+      <c r="F5" s="4">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4">
+        <v>3</v>
+      </c>
+      <c r="H5" s="4">
+        <v>2</v>
+      </c>
+      <c r="I5" s="4">
+        <v>2</v>
+      </c>
+      <c r="J5" s="4">
+        <v>2</v>
+      </c>
+      <c r="K5" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="L5" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="M5" s="11">
+        <v>1</v>
+      </c>
+      <c r="N5" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>2</v>
+      </c>
+      <c r="R5" s="4"/>
+      <c r="S5" s="6"/>
+    </row>
+    <row r="6" customFormat="1" ht="28" spans="1:19">
+      <c r="A6" s="6">
+        <v>910</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="4">
+        <v>25</v>
+      </c>
+      <c r="E6" s="4">
+        <v>9</v>
+      </c>
+      <c r="F6" s="4">
+        <v>4</v>
+      </c>
+      <c r="G6" s="4">
+        <v>3</v>
+      </c>
+      <c r="H6" s="4">
+        <v>2</v>
+      </c>
+      <c r="I6" s="4">
+        <v>2</v>
+      </c>
+      <c r="J6" s="4">
+        <v>2</v>
+      </c>
+      <c r="K6" s="11">
+        <v>0.16</v>
+      </c>
+      <c r="L6" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="M6" s="11">
+        <v>1</v>
+      </c>
+      <c r="N6" s="11">
+        <v>0.08</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>2</v>
+      </c>
+      <c r="R6" s="4"/>
+      <c r="S6" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1561,8 +1723,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R3"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2"/>
+  <dimension ref="A1:R6"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
       <c r="A1" s="8" t="s">
@@ -1619,8 +1781,8 @@
       <c r="R1" s="10"/>
     </row>
     <row r="2" ht="28" spans="1:18">
-      <c r="A2" s="6">
-        <v>909</v>
+      <c r="A2" s="12">
+        <v>904</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>17</v>
@@ -1629,7 +1791,7 @@
         <v>18</v>
       </c>
       <c r="D2" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" s="4">
         <v>0</v>
@@ -1673,8 +1835,8 @@
       <c r="R2" s="4"/>
     </row>
     <row r="3" customFormat="1" ht="28" spans="1:18">
-      <c r="A3" s="6">
-        <v>910</v>
+      <c r="A3" s="12">
+        <v>907</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>17</v>
@@ -1683,7 +1845,7 @@
         <v>18</v>
       </c>
       <c r="D3" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E3" s="4">
         <v>0</v>
@@ -1725,6 +1887,168 @@
         <v>0</v>
       </c>
       <c r="R3" s="4"/>
+    </row>
+    <row r="4" ht="28" spans="1:18">
+      <c r="A4" s="12">
+        <v>908</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="4">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="11">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" s="11">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0</v>
+      </c>
+      <c r="R4" s="4"/>
+    </row>
+    <row r="5" ht="28" spans="1:18">
+      <c r="A5" s="12">
+        <v>909</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4">
+        <v>3</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0</v>
+      </c>
+      <c r="K5" s="11">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N5" s="11">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0</v>
+      </c>
+      <c r="R5" s="4"/>
+    </row>
+    <row r="6" customFormat="1" ht="28" spans="1:18">
+      <c r="A6" s="12">
+        <v>910</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="4">
+        <v>7</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="11">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N6" s="11">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1735,8 +2059,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R3"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2"/>
+  <dimension ref="A1:R6"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
       <c r="A1" s="8" t="s">
@@ -1793,8 +2117,8 @@
       <c r="R1" s="10"/>
     </row>
     <row r="2" ht="28" spans="1:18">
-      <c r="A2" s="6">
-        <v>909</v>
+      <c r="A2" s="12">
+        <v>904</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>17</v>
@@ -1803,10 +2127,10 @@
         <v>18</v>
       </c>
       <c r="D2" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="4">
         <v>0</v>
@@ -1847,8 +2171,8 @@
       <c r="R2" s="4"/>
     </row>
     <row r="3" customFormat="1" ht="28" spans="1:18">
-      <c r="A3" s="6">
-        <v>910</v>
+      <c r="A3" s="12">
+        <v>907</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>17</v>
@@ -1857,10 +2181,10 @@
         <v>18</v>
       </c>
       <c r="D3" s="4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E3" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="4">
         <v>0</v>
@@ -1899,6 +2223,168 @@
         <v>0</v>
       </c>
       <c r="R3" s="4"/>
+    </row>
+    <row r="4" ht="28" spans="1:18">
+      <c r="A4" s="12">
+        <v>908</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="4">
+        <v>4</v>
+      </c>
+      <c r="E4" s="4">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="11">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" s="11">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0</v>
+      </c>
+      <c r="R4" s="4"/>
+    </row>
+    <row r="5" ht="28" spans="1:18">
+      <c r="A5" s="6">
+        <v>909</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4">
+        <v>4</v>
+      </c>
+      <c r="E5" s="4">
+        <v>2</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0</v>
+      </c>
+      <c r="K5" s="11">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N5" s="11">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0</v>
+      </c>
+      <c r="R5" s="4"/>
+    </row>
+    <row r="6" customFormat="1" ht="28" spans="1:18">
+      <c r="A6" s="6">
+        <v>910</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="4">
+        <v>7</v>
+      </c>
+      <c r="E6" s="4">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="11">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N6" s="11">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1909,8 +2395,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R3"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="2"/>
+  <dimension ref="A1:R6"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
       <c r="A1" s="8" t="s">
@@ -1966,9 +2452,9 @@
       </c>
       <c r="R1" s="10"/>
     </row>
-    <row r="2" ht="28" spans="1:18">
+    <row r="2" customFormat="1" ht="28" spans="1:18">
       <c r="A2" s="6">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>17</v>
@@ -1977,13 +2463,13 @@
         <v>18</v>
       </c>
       <c r="D2" s="4">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E2" s="4">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F2" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" s="4">
         <v>2</v>
@@ -1992,22 +2478,22 @@
         <v>2</v>
       </c>
       <c r="I2" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K2" s="11">
-        <v>0.15</v>
+        <v>0.1818</v>
       </c>
       <c r="L2" s="11">
-        <v>1.3333</v>
+        <v>1</v>
       </c>
       <c r="M2" s="11">
         <v>1</v>
       </c>
       <c r="N2" s="11">
-        <v>0.2</v>
+        <v>0.1818</v>
       </c>
       <c r="O2" s="4">
         <v>0</v>
@@ -2016,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="Q2" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R2" s="4"/>
     </row>
     <row r="3" customFormat="1" ht="28" spans="1:18">
-      <c r="A3" s="12" t="s">
-        <v>20</v>
+      <c r="A3" s="12">
+        <v>907</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>17</v>
@@ -2031,48 +2517,210 @@
         <v>18</v>
       </c>
       <c r="D3" s="4">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E3" s="4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" s="4">
+        <v>2</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4">
+        <v>2</v>
+      </c>
+      <c r="I3" s="4">
         <v>3</v>
       </c>
-      <c r="G3" s="4">
-        <v>2</v>
-      </c>
-      <c r="H3" s="4">
-        <v>2</v>
-      </c>
-      <c r="I3" s="4">
-        <v>4</v>
-      </c>
       <c r="J3" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3" s="11">
-        <v>0.125</v>
+        <v>0.1333</v>
       </c>
       <c r="L3" s="11">
-        <v>1.3333</v>
+        <v>1.5</v>
       </c>
       <c r="M3" s="11">
         <v>1</v>
       </c>
       <c r="N3" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="O3" s="4">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>3</v>
+      </c>
+      <c r="R3" s="4"/>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:18">
+      <c r="A4" s="6">
+        <v>908</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="4">
+        <v>20</v>
+      </c>
+      <c r="E4" s="4">
+        <v>11</v>
+      </c>
+      <c r="F4" s="4">
+        <v>3</v>
+      </c>
+      <c r="G4" s="4">
+        <v>2</v>
+      </c>
+      <c r="H4" s="4">
+        <v>2</v>
+      </c>
+      <c r="I4" s="4">
+        <v>4</v>
+      </c>
+      <c r="J4" s="4">
+        <v>4</v>
+      </c>
+      <c r="K4" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="L4" s="11">
+        <v>1.3333</v>
+      </c>
+      <c r="M4" s="11">
+        <v>1</v>
+      </c>
+      <c r="N4" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>4</v>
+      </c>
+      <c r="R4" s="4"/>
+    </row>
+    <row r="5" customFormat="1" ht="28" spans="1:18">
+      <c r="A5" s="6">
+        <v>909</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4">
+        <v>20</v>
+      </c>
+      <c r="E5" s="4">
+        <v>11</v>
+      </c>
+      <c r="F5" s="4">
+        <v>3</v>
+      </c>
+      <c r="G5" s="4">
+        <v>2</v>
+      </c>
+      <c r="H5" s="4">
+        <v>2</v>
+      </c>
+      <c r="I5" s="4">
+        <v>4</v>
+      </c>
+      <c r="J5" s="4">
+        <v>4</v>
+      </c>
+      <c r="K5" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="L5" s="11">
+        <v>1.3333</v>
+      </c>
+      <c r="M5" s="11">
+        <v>1</v>
+      </c>
+      <c r="N5" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>4</v>
+      </c>
+      <c r="R5" s="4"/>
+    </row>
+    <row r="6" customFormat="1" ht="28" spans="1:18">
+      <c r="A6" s="12">
+        <v>910</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="4">
+        <v>24</v>
+      </c>
+      <c r="E6" s="4">
+        <v>11</v>
+      </c>
+      <c r="F6" s="4">
+        <v>3</v>
+      </c>
+      <c r="G6" s="4">
+        <v>2</v>
+      </c>
+      <c r="H6" s="4">
+        <v>2</v>
+      </c>
+      <c r="I6" s="4">
+        <v>4</v>
+      </c>
+      <c r="J6" s="4">
+        <v>4</v>
+      </c>
+      <c r="K6" s="11">
+        <v>0.125</v>
+      </c>
+      <c r="L6" s="11">
+        <v>1.3333</v>
+      </c>
+      <c r="M6" s="11">
+        <v>1</v>
+      </c>
+      <c r="N6" s="11">
         <v>0.1667</v>
       </c>
-      <c r="O3" s="4">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="4">
+      <c r="O6" s="4">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4">
         <v>4</v>
       </c>
-      <c r="R3" s="4"/>
+      <c r="R6" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2091,28 +2739,28 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>0</v>
@@ -2132,25 +2780,25 @@
         <v>1152836023</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="D2" s="5">
         <v>46272.7013888889</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="I2" s="6">
         <v>909</v>
@@ -2170,25 +2818,25 @@
         <v>1136806429</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="D3" s="5">
         <v>46272.4770833333</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="I3" s="6">
         <v>909</v>
@@ -2208,25 +2856,25 @@
         <v>1138408935</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="D4" s="5">
         <v>46268.8833333333</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="I4" s="6">
         <v>909</v>
@@ -2246,25 +2894,25 @@
         <v>598907779</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="D5" s="5">
         <v>46268.6451388889</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="I5" s="6">
         <v>909</v>
@@ -2284,25 +2932,25 @@
         <v>1146073421</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="D6" s="5">
         <v>46268.6388888889</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="I6" s="6">
         <v>909</v>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="34">
   <si>
     <t>日期</t>
   </si>
@@ -816,16 +816,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -835,9 +832,6 @@
     <xf numFmtId="22" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -849,6 +843,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1381,338 +1378,393 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5"/>
+  <dimension ref="A1:S7"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" ht="28" spans="1:19">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="9" t="s">
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="10"/>
-      <c r="S1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="6"/>
     </row>
     <row r="2" ht="28" spans="1:19">
-      <c r="A2" s="6">
+      <c r="A2" s="9">
         <v>904</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>7</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <v>4</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="3">
         <v>1</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="3">
         <v>1</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="3">
         <v>1</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="3">
         <v>1</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="3">
         <v>1</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="10">
         <v>0.1429</v>
       </c>
-      <c r="L2" s="11">
+      <c r="L2" s="10">
         <v>1</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="10">
         <v>1</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="10">
         <v>0.1429</v>
       </c>
-      <c r="O2" s="4">
-        <v>0</v>
-      </c>
-      <c r="P2" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="4">
+      <c r="O2" s="3">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="3">
         <v>1</v>
       </c>
-      <c r="R2" s="4"/>
-      <c r="S2" s="6"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="9"/>
     </row>
     <row r="3" customFormat="1" ht="28" spans="1:19">
-      <c r="A3" s="6">
+      <c r="A3" s="9">
         <v>907</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>13</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>6</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="3">
         <v>3</v>
       </c>
-      <c r="G3" s="4">
-        <v>2</v>
-      </c>
-      <c r="H3" s="4">
-        <v>2</v>
-      </c>
-      <c r="I3" s="4">
-        <v>2</v>
-      </c>
-      <c r="J3" s="4">
-        <v>2</v>
-      </c>
-      <c r="K3" s="11">
+      <c r="G3" s="3">
+        <v>2</v>
+      </c>
+      <c r="H3" s="3">
+        <v>2</v>
+      </c>
+      <c r="I3" s="3">
+        <v>2</v>
+      </c>
+      <c r="J3" s="3">
+        <v>2</v>
+      </c>
+      <c r="K3" s="10">
         <v>0.2308</v>
       </c>
-      <c r="L3" s="11">
+      <c r="L3" s="10">
         <v>0.6667</v>
       </c>
-      <c r="M3" s="11">
+      <c r="M3" s="10">
         <v>1</v>
       </c>
-      <c r="N3" s="11">
+      <c r="N3" s="10">
         <v>0.1538</v>
       </c>
-      <c r="O3" s="4">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>2</v>
-      </c>
-      <c r="R3" s="4"/>
-      <c r="S3" s="6"/>
+      <c r="O3" s="3">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>2</v>
+      </c>
+      <c r="R3" s="3"/>
+      <c r="S3" s="9"/>
     </row>
     <row r="4" ht="28" spans="1:19">
-      <c r="A4" s="6">
+      <c r="A4" s="9">
         <v>908</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>20</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>9</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <v>4</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="3">
         <v>3</v>
       </c>
-      <c r="H4" s="4">
-        <v>2</v>
-      </c>
-      <c r="I4" s="4">
-        <v>2</v>
-      </c>
-      <c r="J4" s="4">
-        <v>2</v>
-      </c>
-      <c r="K4" s="11">
+      <c r="H4" s="3">
+        <v>2</v>
+      </c>
+      <c r="I4" s="3">
+        <v>2</v>
+      </c>
+      <c r="J4" s="3">
+        <v>2</v>
+      </c>
+      <c r="K4" s="10">
         <v>0.2</v>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="10">
         <v>0.5</v>
       </c>
-      <c r="M4" s="11">
+      <c r="M4" s="10">
         <v>1</v>
       </c>
-      <c r="N4" s="11">
+      <c r="N4" s="10">
         <v>0.1</v>
       </c>
-      <c r="O4" s="4">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4">
-        <v>2</v>
-      </c>
-      <c r="R4" s="4"/>
-      <c r="S4" s="6"/>
+      <c r="O4" s="3">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>2</v>
+      </c>
+      <c r="R4" s="3"/>
+      <c r="S4" s="9"/>
     </row>
     <row r="5" ht="28" spans="1:19">
-      <c r="A5" s="6">
+      <c r="A5" s="9">
         <v>909</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>20</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>9</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>4</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="3">
         <v>3</v>
       </c>
-      <c r="H5" s="4">
-        <v>2</v>
-      </c>
-      <c r="I5" s="4">
-        <v>2</v>
-      </c>
-      <c r="J5" s="4">
-        <v>2</v>
-      </c>
-      <c r="K5" s="11">
+      <c r="H5" s="3">
+        <v>2</v>
+      </c>
+      <c r="I5" s="3">
+        <v>2</v>
+      </c>
+      <c r="J5" s="3">
+        <v>2</v>
+      </c>
+      <c r="K5" s="10">
         <v>0.2</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="10">
         <v>0.5</v>
       </c>
-      <c r="M5" s="11">
+      <c r="M5" s="10">
         <v>1</v>
       </c>
-      <c r="N5" s="11">
+      <c r="N5" s="10">
         <v>0.1</v>
       </c>
-      <c r="O5" s="4">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>2</v>
-      </c>
-      <c r="R5" s="4"/>
-      <c r="S5" s="6"/>
+      <c r="O5" s="3">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>2</v>
+      </c>
+      <c r="R5" s="3"/>
+      <c r="S5" s="9"/>
     </row>
     <row r="6" customFormat="1" ht="28" spans="1:19">
-      <c r="A6" s="6">
+      <c r="A6" s="9">
         <v>910</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>25</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>9</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>4</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>3</v>
       </c>
-      <c r="H6" s="4">
-        <v>2</v>
-      </c>
-      <c r="I6" s="4">
-        <v>2</v>
-      </c>
-      <c r="J6" s="4">
-        <v>2</v>
-      </c>
-      <c r="K6" s="11">
+      <c r="H6" s="3">
+        <v>2</v>
+      </c>
+      <c r="I6" s="3">
+        <v>2</v>
+      </c>
+      <c r="J6" s="3">
+        <v>2</v>
+      </c>
+      <c r="K6" s="10">
         <v>0.16</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="10">
         <v>0.5</v>
       </c>
-      <c r="M6" s="11">
+      <c r="M6" s="10">
         <v>1</v>
       </c>
-      <c r="N6" s="11">
+      <c r="N6" s="10">
         <v>0.08</v>
       </c>
-      <c r="O6" s="4">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4">
-        <v>2</v>
-      </c>
-      <c r="R6" s="4"/>
-      <c r="S6" s="6"/>
+      <c r="O6" s="3">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>2</v>
+      </c>
+      <c r="R6" s="3"/>
+      <c r="S6" s="9"/>
+    </row>
+    <row r="7" customFormat="1" ht="28" spans="1:19">
+      <c r="A7" s="9">
+        <v>911</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="3">
+        <v>28</v>
+      </c>
+      <c r="E7" s="3">
+        <v>10</v>
+      </c>
+      <c r="F7" s="3">
+        <v>5</v>
+      </c>
+      <c r="G7" s="3">
+        <v>4</v>
+      </c>
+      <c r="H7" s="3">
+        <v>3</v>
+      </c>
+      <c r="I7" s="3">
+        <v>3</v>
+      </c>
+      <c r="J7" s="3">
+        <v>3</v>
+      </c>
+      <c r="K7" s="10">
+        <v>0.1786</v>
+      </c>
+      <c r="L7" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="M7" s="10">
+        <v>1</v>
+      </c>
+      <c r="N7" s="10">
+        <v>0.1071</v>
+      </c>
+      <c r="O7" s="3">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>3</v>
+      </c>
+      <c r="R7" s="3"/>
+      <c r="S7" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1723,332 +1775,386 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5"/>
+  <dimension ref="A1:R7"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="9" t="s">
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="10"/>
+      <c r="R1" s="8"/>
     </row>
     <row r="2" ht="28" spans="1:18">
-      <c r="A2" s="12">
+      <c r="A2" s="11">
         <v>904</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>1</v>
       </c>
-      <c r="E2" s="4">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4">
-        <v>0</v>
-      </c>
-      <c r="I2" s="4">
-        <v>0</v>
-      </c>
-      <c r="J2" s="4">
-        <v>0</v>
-      </c>
-      <c r="K2" s="11">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4" t="s">
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0</v>
+      </c>
+      <c r="K2" s="10">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="11">
-        <v>0</v>
-      </c>
-      <c r="O2" s="4">
-        <v>0</v>
-      </c>
-      <c r="P2" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="4">
-        <v>0</v>
-      </c>
-      <c r="R2" s="4"/>
+      <c r="N2" s="10">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>0</v>
+      </c>
+      <c r="R2" s="3"/>
     </row>
     <row r="3" customFormat="1" ht="28" spans="1:18">
-      <c r="A3" s="12">
+      <c r="A3" s="11">
         <v>907</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="4">
-        <v>2</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4">
-        <v>0</v>
-      </c>
-      <c r="K3" s="11">
-        <v>0</v>
-      </c>
-      <c r="L3" s="4" t="s">
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0</v>
+      </c>
+      <c r="K3" s="10">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="11">
-        <v>0</v>
-      </c>
-      <c r="O3" s="4">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>0</v>
-      </c>
-      <c r="R3" s="4"/>
+      <c r="N3" s="10">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>0</v>
+      </c>
+      <c r="R3" s="3"/>
     </row>
     <row r="4" ht="28" spans="1:18">
-      <c r="A4" s="12">
+      <c r="A4" s="11">
         <v>908</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>3</v>
       </c>
-      <c r="E4" s="4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="11">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4" t="s">
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0</v>
+      </c>
+      <c r="K4" s="10">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="11">
-        <v>0</v>
-      </c>
-      <c r="O4" s="4">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4">
-        <v>0</v>
-      </c>
-      <c r="R4" s="4"/>
+      <c r="N4" s="10">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>0</v>
+      </c>
+      <c r="R4" s="3"/>
     </row>
     <row r="5" ht="28" spans="1:18">
-      <c r="A5" s="12">
+      <c r="A5" s="11">
         <v>909</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>3</v>
       </c>
-      <c r="E5" s="4">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4">
-        <v>0</v>
-      </c>
-      <c r="K5" s="11">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4" t="s">
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0</v>
+      </c>
+      <c r="K5" s="10">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N5" s="11">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>0</v>
-      </c>
-      <c r="R5" s="4"/>
+      <c r="N5" s="10">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3"/>
     </row>
     <row r="6" customFormat="1" ht="28" spans="1:18">
-      <c r="A6" s="12">
+      <c r="A6" s="11">
         <v>910</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>7</v>
       </c>
-      <c r="E6" s="4">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4">
-        <v>0</v>
-      </c>
-      <c r="I6" s="4">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4">
-        <v>0</v>
-      </c>
-      <c r="K6" s="11">
-        <v>0</v>
-      </c>
-      <c r="L6" s="4" t="s">
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0</v>
+      </c>
+      <c r="K6" s="10">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N6" s="11">
-        <v>0</v>
-      </c>
-      <c r="O6" s="4">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4">
-        <v>0</v>
-      </c>
-      <c r="R6" s="4"/>
+      <c r="N6" s="10">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3"/>
+    </row>
+    <row r="7" customFormat="1" ht="28" spans="1:18">
+      <c r="A7" s="11">
+        <v>911</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="3">
+        <v>7</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0</v>
+      </c>
+      <c r="K7" s="10">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="10">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2059,332 +2165,386 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5"/>
+  <dimension ref="A1:R7"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="9" t="s">
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="10"/>
+      <c r="R1" s="8"/>
     </row>
     <row r="2" ht="28" spans="1:18">
-      <c r="A2" s="12">
+      <c r="A2" s="11">
         <v>904</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>3</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <v>1</v>
       </c>
-      <c r="F2" s="4">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4">
-        <v>0</v>
-      </c>
-      <c r="I2" s="4">
-        <v>0</v>
-      </c>
-      <c r="J2" s="4">
-        <v>0</v>
-      </c>
-      <c r="K2" s="11">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4" t="s">
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0</v>
+      </c>
+      <c r="K2" s="10">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="11">
-        <v>0</v>
-      </c>
-      <c r="O2" s="4">
-        <v>0</v>
-      </c>
-      <c r="P2" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="4">
-        <v>0</v>
-      </c>
-      <c r="R2" s="4"/>
+      <c r="N2" s="10">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>0</v>
+      </c>
+      <c r="R2" s="3"/>
     </row>
     <row r="3" customFormat="1" ht="28" spans="1:18">
-      <c r="A3" s="12">
+      <c r="A3" s="11">
         <v>907</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>3</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>1</v>
       </c>
-      <c r="F3" s="4">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4">
-        <v>0</v>
-      </c>
-      <c r="K3" s="11">
-        <v>0</v>
-      </c>
-      <c r="L3" s="4" t="s">
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0</v>
+      </c>
+      <c r="K3" s="10">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="11">
-        <v>0</v>
-      </c>
-      <c r="O3" s="4">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>0</v>
-      </c>
-      <c r="R3" s="4"/>
+      <c r="N3" s="10">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>0</v>
+      </c>
+      <c r="R3" s="3"/>
     </row>
     <row r="4" ht="28" spans="1:18">
-      <c r="A4" s="12">
+      <c r="A4" s="11">
         <v>908</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>4</v>
       </c>
-      <c r="E4" s="4">
-        <v>2</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="11">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4" t="s">
+      <c r="E4" s="3">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0</v>
+      </c>
+      <c r="K4" s="10">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="11">
-        <v>0</v>
-      </c>
-      <c r="O4" s="4">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4">
-        <v>0</v>
-      </c>
-      <c r="R4" s="4"/>
+      <c r="N4" s="10">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>0</v>
+      </c>
+      <c r="R4" s="3"/>
     </row>
     <row r="5" ht="28" spans="1:18">
-      <c r="A5" s="6">
+      <c r="A5" s="9">
         <v>909</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>4</v>
       </c>
-      <c r="E5" s="4">
-        <v>2</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4">
-        <v>0</v>
-      </c>
-      <c r="K5" s="11">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4" t="s">
+      <c r="E5" s="3">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0</v>
+      </c>
+      <c r="K5" s="10">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N5" s="11">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>0</v>
-      </c>
-      <c r="R5" s="4"/>
+      <c r="N5" s="10">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3"/>
     </row>
     <row r="6" customFormat="1" ht="28" spans="1:18">
-      <c r="A6" s="6">
+      <c r="A6" s="9">
         <v>910</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>7</v>
       </c>
-      <c r="E6" s="4">
-        <v>2</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4">
-        <v>0</v>
-      </c>
-      <c r="I6" s="4">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4">
-        <v>0</v>
-      </c>
-      <c r="K6" s="11">
-        <v>0</v>
-      </c>
-      <c r="L6" s="4" t="s">
+      <c r="E6" s="3">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0</v>
+      </c>
+      <c r="K6" s="10">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N6" s="11">
-        <v>0</v>
-      </c>
-      <c r="O6" s="4">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4">
-        <v>0</v>
-      </c>
-      <c r="R6" s="4"/>
+      <c r="N6" s="10">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3"/>
+    </row>
+    <row r="7" customFormat="1" ht="28" spans="1:18">
+      <c r="A7" s="9">
+        <v>911</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="3">
+        <v>7</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0</v>
+      </c>
+      <c r="K7" s="10">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="10">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2395,332 +2555,386 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5"/>
+  <dimension ref="A1:R7"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="9" t="s">
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="10"/>
+      <c r="R1" s="8"/>
     </row>
     <row r="2" customFormat="1" ht="28" spans="1:18">
-      <c r="A2" s="6">
+      <c r="A2" s="9">
         <v>904</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>11</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <v>6</v>
       </c>
-      <c r="F2" s="4">
-        <v>2</v>
-      </c>
-      <c r="G2" s="4">
-        <v>2</v>
-      </c>
-      <c r="H2" s="4">
-        <v>2</v>
-      </c>
-      <c r="I2" s="4">
-        <v>2</v>
-      </c>
-      <c r="J2" s="4">
-        <v>2</v>
-      </c>
-      <c r="K2" s="11">
+      <c r="F2" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2" s="3">
+        <v>2</v>
+      </c>
+      <c r="H2" s="3">
+        <v>2</v>
+      </c>
+      <c r="I2" s="3">
+        <v>2</v>
+      </c>
+      <c r="J2" s="3">
+        <v>2</v>
+      </c>
+      <c r="K2" s="10">
         <v>0.1818</v>
       </c>
-      <c r="L2" s="11">
+      <c r="L2" s="10">
         <v>1</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="10">
         <v>1</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="10">
         <v>0.1818</v>
       </c>
-      <c r="O2" s="4">
-        <v>0</v>
-      </c>
-      <c r="P2" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="4">
-        <v>2</v>
-      </c>
-      <c r="R2" s="4"/>
+      <c r="O2" s="3">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>2</v>
+      </c>
+      <c r="R2" s="3"/>
     </row>
     <row r="3" customFormat="1" ht="28" spans="1:18">
-      <c r="A3" s="12">
+      <c r="A3" s="11">
         <v>907</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>15</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>9</v>
       </c>
-      <c r="F3" s="4">
-        <v>2</v>
-      </c>
-      <c r="G3" s="4">
-        <v>2</v>
-      </c>
-      <c r="H3" s="4">
-        <v>2</v>
-      </c>
-      <c r="I3" s="4">
+      <c r="F3" s="3">
+        <v>2</v>
+      </c>
+      <c r="G3" s="3">
+        <v>2</v>
+      </c>
+      <c r="H3" s="3">
+        <v>2</v>
+      </c>
+      <c r="I3" s="3">
         <v>3</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="3">
         <v>3</v>
       </c>
-      <c r="K3" s="11">
+      <c r="K3" s="10">
         <v>0.1333</v>
       </c>
-      <c r="L3" s="11">
+      <c r="L3" s="10">
         <v>1.5</v>
       </c>
-      <c r="M3" s="11">
+      <c r="M3" s="10">
         <v>1</v>
       </c>
-      <c r="N3" s="11">
+      <c r="N3" s="10">
         <v>0.2</v>
       </c>
-      <c r="O3" s="4">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="4">
+      <c r="O3" s="3">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="3">
         <v>3</v>
       </c>
-      <c r="R3" s="4"/>
+      <c r="R3" s="3"/>
     </row>
     <row r="4" customFormat="1" ht="28" spans="1:18">
-      <c r="A4" s="6">
+      <c r="A4" s="9">
         <v>908</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>20</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>11</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <v>3</v>
       </c>
-      <c r="G4" s="4">
-        <v>2</v>
-      </c>
-      <c r="H4" s="4">
-        <v>2</v>
-      </c>
-      <c r="I4" s="4">
+      <c r="G4" s="3">
+        <v>2</v>
+      </c>
+      <c r="H4" s="3">
+        <v>2</v>
+      </c>
+      <c r="I4" s="3">
         <v>4</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="3">
         <v>4</v>
       </c>
-      <c r="K4" s="11">
+      <c r="K4" s="10">
         <v>0.15</v>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="10">
         <v>1.3333</v>
       </c>
-      <c r="M4" s="11">
+      <c r="M4" s="10">
         <v>1</v>
       </c>
-      <c r="N4" s="11">
+      <c r="N4" s="10">
         <v>0.2</v>
       </c>
-      <c r="O4" s="4">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4">
+      <c r="O4" s="3">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="3">
         <v>4</v>
       </c>
-      <c r="R4" s="4"/>
+      <c r="R4" s="3"/>
     </row>
     <row r="5" customFormat="1" ht="28" spans="1:18">
-      <c r="A5" s="6">
+      <c r="A5" s="9">
         <v>909</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>20</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>11</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>3</v>
       </c>
-      <c r="G5" s="4">
-        <v>2</v>
-      </c>
-      <c r="H5" s="4">
-        <v>2</v>
-      </c>
-      <c r="I5" s="4">
+      <c r="G5" s="3">
+        <v>2</v>
+      </c>
+      <c r="H5" s="3">
+        <v>2</v>
+      </c>
+      <c r="I5" s="3">
         <v>4</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="3">
         <v>4</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="10">
         <v>0.15</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="10">
         <v>1.3333</v>
       </c>
-      <c r="M5" s="11">
+      <c r="M5" s="10">
         <v>1</v>
       </c>
-      <c r="N5" s="11">
+      <c r="N5" s="10">
         <v>0.2</v>
       </c>
-      <c r="O5" s="4">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4">
+      <c r="O5" s="3">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3">
         <v>4</v>
       </c>
-      <c r="R5" s="4"/>
+      <c r="R5" s="3"/>
     </row>
     <row r="6" customFormat="1" ht="28" spans="1:18">
-      <c r="A6" s="12">
+      <c r="A6" s="11">
         <v>910</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>24</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>11</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>3</v>
       </c>
-      <c r="G6" s="4">
-        <v>2</v>
-      </c>
-      <c r="H6" s="4">
-        <v>2</v>
-      </c>
-      <c r="I6" s="4">
+      <c r="G6" s="3">
+        <v>2</v>
+      </c>
+      <c r="H6" s="3">
+        <v>2</v>
+      </c>
+      <c r="I6" s="3">
         <v>4</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="3">
         <v>4</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="10">
         <v>0.125</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="10">
         <v>1.3333</v>
       </c>
-      <c r="M6" s="11">
+      <c r="M6" s="10">
         <v>1</v>
       </c>
-      <c r="N6" s="11">
+      <c r="N6" s="10">
         <v>0.1667</v>
       </c>
-      <c r="O6" s="4">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4">
+      <c r="O6" s="3">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3">
         <v>4</v>
       </c>
-      <c r="R6" s="4"/>
+      <c r="R6" s="3"/>
+    </row>
+    <row r="7" customFormat="1" ht="28" spans="1:18">
+      <c r="A7" s="11">
+        <v>911</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="3">
+        <v>24</v>
+      </c>
+      <c r="E7" s="3">
+        <v>11</v>
+      </c>
+      <c r="F7" s="3">
+        <v>3</v>
+      </c>
+      <c r="G7" s="3">
+        <v>2</v>
+      </c>
+      <c r="H7" s="3">
+        <v>2</v>
+      </c>
+      <c r="I7" s="3">
+        <v>4</v>
+      </c>
+      <c r="J7" s="3">
+        <v>4</v>
+      </c>
+      <c r="K7" s="10">
+        <v>0.125</v>
+      </c>
+      <c r="L7" s="10">
+        <v>1.3333</v>
+      </c>
+      <c r="M7" s="10">
+        <v>1</v>
+      </c>
+      <c r="N7" s="10">
+        <v>0.1667</v>
+      </c>
+      <c r="O7" s="3">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>4</v>
+      </c>
+      <c r="R7" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2731,13 +2945,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5"/>
+  <dimension ref="A1:Q8"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="7"/>
   <cols>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="1" max="1" width="10.7692307692308"/>
+    <col min="4" max="4" width="15.2307692307692" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -2762,208 +2977,260 @@
       <c r="H1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-    </row>
-    <row r="2" ht="28" spans="1:18">
-      <c r="A2" s="4">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" ht="28" spans="1:17">
+      <c r="A2" s="3">
+        <v>1153370608</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="4">
+        <v>46276.5826388889</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+    </row>
+    <row r="3" ht="28" spans="1:17">
+      <c r="A3" s="3">
+        <v>1015710983</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="4">
+        <v>46276.4298611111</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+    </row>
+    <row r="4" ht="28" spans="1:17">
+      <c r="A4" s="3">
         <v>1152836023</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D4" s="4">
         <v>46272.7013888889</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="6">
-        <v>909</v>
-      </c>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-    </row>
-    <row r="3" ht="28" spans="1:18">
-      <c r="A3" s="4">
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+    </row>
+    <row r="5" ht="28" spans="1:17">
+      <c r="A5" s="3">
         <v>1136806429</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D5" s="4">
         <v>46272.4770833333</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="6">
-        <v>909</v>
-      </c>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-    </row>
-    <row r="4" ht="28" spans="1:18">
-      <c r="A4" s="4">
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+    </row>
+    <row r="6" ht="28" spans="1:17">
+      <c r="A6" s="3">
         <v>1138408935</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D6" s="4">
         <v>46268.8833333333</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="6">
-        <v>909</v>
-      </c>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-    </row>
-    <row r="5" ht="28" spans="1:18">
-      <c r="A5" s="4">
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+    </row>
+    <row r="7" ht="28" spans="1:17">
+      <c r="A7" s="3">
         <v>598907779</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D7" s="4">
         <v>46268.6451388889</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="6">
-        <v>909</v>
-      </c>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-    </row>
-    <row r="6" ht="28" spans="1:18">
-      <c r="A6" s="4">
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+    </row>
+    <row r="8" ht="28" spans="1:17">
+      <c r="A8" s="3">
         <v>1146073421</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D8" s="4">
         <v>46268.6388888889</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="6">
-        <v>909</v>
-      </c>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2972,6 +3239,8 @@
     <hyperlink ref="E4" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
     <hyperlink ref="E5" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
     <hyperlink ref="E6" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
+    <hyperlink ref="E7" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
+    <hyperlink ref="E8" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="34">
   <si>
     <t>日期</t>
   </si>
@@ -1378,8 +1378,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S7"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <dimension ref="A1:S8"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="7"/>
   <sheetData>
     <row r="1" ht="28" spans="1:19">
       <c r="A1" s="6" t="s">
@@ -1765,6 +1765,61 @@
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="9"/>
+    </row>
+    <row r="8" customFormat="1" ht="28" spans="1:19">
+      <c r="A8" s="9">
+        <v>914</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="3">
+        <v>34</v>
+      </c>
+      <c r="E8" s="3">
+        <v>11</v>
+      </c>
+      <c r="F8" s="3">
+        <v>6</v>
+      </c>
+      <c r="G8" s="3">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3">
+        <v>3</v>
+      </c>
+      <c r="K8" s="10">
+        <v>0.1765</v>
+      </c>
+      <c r="L8" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="M8" s="10">
+        <v>1</v>
+      </c>
+      <c r="N8" s="10">
+        <v>0.0882</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+      <c r="S8" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1775,8 +1830,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R7"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <dimension ref="A1:R8"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="7"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
       <c r="A1" s="6" t="s">
@@ -2155,6 +2210,60 @@
         <v>0</v>
       </c>
       <c r="R7" s="3"/>
+    </row>
+    <row r="8" customFormat="1" ht="28" spans="1:18">
+      <c r="A8" s="11">
+        <v>914</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="3">
+        <v>7</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="10">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N8" s="10">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2165,8 +2274,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R7"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <dimension ref="A1:R8"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="7"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
       <c r="A1" s="6" t="s">
@@ -2545,6 +2654,60 @@
         <v>0</v>
       </c>
       <c r="R7" s="3"/>
+    </row>
+    <row r="8" customFormat="1" ht="28" spans="1:18">
+      <c r="A8" s="9">
+        <v>914</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="3">
+        <v>7</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="10">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N8" s="10">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2555,8 +2718,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R7"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <dimension ref="A1:R8"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="7"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
       <c r="A1" s="6" t="s">
@@ -2935,6 +3098,60 @@
         <v>4</v>
       </c>
       <c r="R7" s="3"/>
+    </row>
+    <row r="8" customFormat="1" ht="28" spans="1:18">
+      <c r="A8" s="11">
+        <v>914</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="3">
+        <v>29</v>
+      </c>
+      <c r="E8" s="3">
+        <v>12</v>
+      </c>
+      <c r="F8" s="3">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
+        <v>5</v>
+      </c>
+      <c r="J8" s="3">
+        <v>5</v>
+      </c>
+      <c r="K8" s="10">
+        <v>0.1379</v>
+      </c>
+      <c r="L8" s="10">
+        <v>1.25</v>
+      </c>
+      <c r="M8" s="10">
+        <v>1</v>
+      </c>
+      <c r="N8" s="10">
+        <v>0.1724</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>5</v>
+      </c>
+      <c r="R8" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -1777,7 +1777,7 @@
         <v>18</v>
       </c>
       <c r="D8" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E8" s="3">
         <v>11</v>
@@ -1798,7 +1798,7 @@
         <v>3</v>
       </c>
       <c r="K8" s="10">
-        <v>0.1765</v>
+        <v>0.1714</v>
       </c>
       <c r="L8" s="10">
         <v>0.5</v>
@@ -1807,7 +1807,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="10">
-        <v>0.0882</v>
+        <v>0.0857</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="34">
   <si>
     <t>日期</t>
   </si>
@@ -1378,8 +1378,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S8"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="7"/>
+  <dimension ref="A1:S9"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:19">
       <c r="A1" s="6" t="s">
@@ -1820,6 +1820,61 @@
       </c>
       <c r="R8" s="3"/>
       <c r="S8" s="9"/>
+    </row>
+    <row r="9" customFormat="1" ht="28" spans="1:19">
+      <c r="A9" s="9">
+        <v>915</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="3">
+        <v>35</v>
+      </c>
+      <c r="E9" s="3">
+        <v>11</v>
+      </c>
+      <c r="F9" s="3">
+        <v>6</v>
+      </c>
+      <c r="G9" s="3">
+        <v>4</v>
+      </c>
+      <c r="H9" s="3">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3">
+        <v>3</v>
+      </c>
+      <c r="K9" s="10">
+        <v>0.1714</v>
+      </c>
+      <c r="L9" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="M9" s="10">
+        <v>1</v>
+      </c>
+      <c r="N9" s="10">
+        <v>0.0857</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+      <c r="S9" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1830,8 +1885,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R8"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="7"/>
+  <dimension ref="A1:R9"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
       <c r="A1" s="6" t="s">
@@ -2264,6 +2319,60 @@
         <v>0</v>
       </c>
       <c r="R8" s="3"/>
+    </row>
+    <row r="9" customFormat="1" ht="28" spans="1:18">
+      <c r="A9" s="11">
+        <v>915</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="3">
+        <v>7</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="10">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N9" s="10">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2274,8 +2383,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R8"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="7"/>
+  <dimension ref="A1:R9"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
       <c r="A1" s="6" t="s">
@@ -2708,6 +2817,60 @@
         <v>0</v>
       </c>
       <c r="R8" s="3"/>
+    </row>
+    <row r="9" customFormat="1" ht="28" spans="1:18">
+      <c r="A9" s="9">
+        <v>915</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="3">
+        <v>7</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="10">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N9" s="10">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2718,8 +2881,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R8"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="7"/>
+  <dimension ref="A1:R9"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
       <c r="A1" s="6" t="s">
@@ -3152,6 +3315,58 @@
         <v>5</v>
       </c>
       <c r="R8" s="3"/>
+    </row>
+    <row r="9" customFormat="1" ht="28" spans="1:18">
+      <c r="A9" s="11"/>
+      <c r="B9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="3">
+        <v>32</v>
+      </c>
+      <c r="E9" s="3">
+        <v>12</v>
+      </c>
+      <c r="F9" s="3">
+        <v>4</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3">
+        <v>5</v>
+      </c>
+      <c r="J9" s="3">
+        <v>5</v>
+      </c>
+      <c r="K9" s="10">
+        <v>0.125</v>
+      </c>
+      <c r="L9" s="10">
+        <v>1.25</v>
+      </c>
+      <c r="M9" s="10">
+        <v>1</v>
+      </c>
+      <c r="N9" s="10">
+        <v>0.1562</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12640" activeTab="4"/>
+    <workbookView windowWidth="29400" windowHeight="12640" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="校边店海报1" sheetId="1" r:id="rId1"/>
@@ -3317,7 +3317,9 @@
       <c r="R8" s="3"/>
     </row>
     <row r="9" customFormat="1" ht="28" spans="1:18">
-      <c r="A9" s="11"/>
+      <c r="A9" s="11">
+        <v>915</v>
+      </c>
       <c r="B9" s="3" t="s">
         <v>17</v>
       </c>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12640" activeTab="3"/>
+    <workbookView windowWidth="29400" windowHeight="12640" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="校边店海报1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="34">
   <si>
     <t>日期</t>
   </si>
@@ -1378,7 +1378,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:19">
@@ -1875,6 +1875,61 @@
       </c>
       <c r="R9" s="3"/>
       <c r="S9" s="9"/>
+    </row>
+    <row r="10" customFormat="1" ht="28" spans="1:19">
+      <c r="A10" s="9">
+        <v>916</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="3">
+        <v>38</v>
+      </c>
+      <c r="E10" s="3">
+        <v>12</v>
+      </c>
+      <c r="F10" s="3">
+        <v>6</v>
+      </c>
+      <c r="G10" s="3">
+        <v>4</v>
+      </c>
+      <c r="H10" s="3">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3">
+        <v>3</v>
+      </c>
+      <c r="K10" s="10">
+        <v>0.1579</v>
+      </c>
+      <c r="L10" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="M10" s="10">
+        <v>1</v>
+      </c>
+      <c r="N10" s="10">
+        <v>0.0789</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+      <c r="S10" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1885,7 +1940,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -2373,6 +2428,60 @@
         <v>0</v>
       </c>
       <c r="R9" s="3"/>
+    </row>
+    <row r="10" customFormat="1" ht="28" spans="1:18">
+      <c r="A10" s="11">
+        <v>916</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="3">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1</v>
+      </c>
+      <c r="K10" s="10">
+        <v>1</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N10" s="10">
+        <v>1</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1</v>
+      </c>
+      <c r="P10" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>1</v>
+      </c>
+      <c r="R10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2383,7 +2492,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -2871,6 +2980,60 @@
         <v>0</v>
       </c>
       <c r="R9" s="3"/>
+    </row>
+    <row r="10" customFormat="1" ht="28" spans="1:18">
+      <c r="A10" s="9">
+        <v>916</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="3">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1</v>
+      </c>
+      <c r="K10" s="10">
+        <v>1</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N10" s="10">
+        <v>1</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1</v>
+      </c>
+      <c r="P10" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>1</v>
+      </c>
+      <c r="R10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2881,7 +3044,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -3369,6 +3532,60 @@
         <v>5</v>
       </c>
       <c r="R9" s="3"/>
+    </row>
+    <row r="10" customFormat="1" ht="28" spans="1:18">
+      <c r="A10" s="11">
+        <v>916</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="3">
+        <v>34</v>
+      </c>
+      <c r="E10" s="3">
+        <v>12</v>
+      </c>
+      <c r="F10" s="3">
+        <v>4</v>
+      </c>
+      <c r="G10" s="3">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3">
+        <v>5</v>
+      </c>
+      <c r="J10" s="3">
+        <v>5</v>
+      </c>
+      <c r="K10" s="10">
+        <v>0.1176</v>
+      </c>
+      <c r="L10" s="10">
+        <v>1.25</v>
+      </c>
+      <c r="M10" s="10">
+        <v>1</v>
+      </c>
+      <c r="N10" s="10">
+        <v>0.1471</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -2440,28 +2440,28 @@
         <v>18</v>
       </c>
       <c r="D10" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>19</v>
@@ -2470,16 +2470,16 @@
         <v>19</v>
       </c>
       <c r="N10" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" s="3"/>
     </row>
@@ -2992,28 +2992,28 @@
         <v>18</v>
       </c>
       <c r="D10" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>19</v>
@@ -3022,16 +3022,16 @@
         <v>19</v>
       </c>
       <c r="N10" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" s="3"/>
     </row>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12640" activeTab="4"/>
+    <workbookView windowWidth="29400" windowHeight="12640" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="校边店海报1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="34">
   <si>
     <t>日期</t>
   </si>
@@ -1378,7 +1378,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:19">
@@ -1930,6 +1930,61 @@
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="9"/>
+    </row>
+    <row r="11" customFormat="1" ht="28" spans="1:19">
+      <c r="A11" s="9">
+        <v>917</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="3">
+        <v>38</v>
+      </c>
+      <c r="E11" s="3">
+        <v>12</v>
+      </c>
+      <c r="F11" s="3">
+        <v>6</v>
+      </c>
+      <c r="G11" s="3">
+        <v>4</v>
+      </c>
+      <c r="H11" s="3">
+        <v>3</v>
+      </c>
+      <c r="I11" s="3">
+        <v>3</v>
+      </c>
+      <c r="J11" s="3">
+        <v>3</v>
+      </c>
+      <c r="K11" s="10">
+        <v>0.1579</v>
+      </c>
+      <c r="L11" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="M11" s="10">
+        <v>1</v>
+      </c>
+      <c r="N11" s="10">
+        <v>0.0789</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0</v>
+      </c>
+      <c r="P11" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>3</v>
+      </c>
+      <c r="R11" s="3"/>
+      <c r="S11" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1940,7 +1995,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -2482,6 +2537,60 @@
         <v>0</v>
       </c>
       <c r="R10" s="3"/>
+    </row>
+    <row r="11" customFormat="1" ht="28" spans="1:18">
+      <c r="A11" s="11">
+        <v>917</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="3">
+        <v>8</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3">
+        <v>1</v>
+      </c>
+      <c r="K11" s="10">
+        <v>0.125</v>
+      </c>
+      <c r="L11" s="3">
+        <v>1</v>
+      </c>
+      <c r="M11" s="3">
+        <v>1</v>
+      </c>
+      <c r="N11" s="10">
+        <v>0.125</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0</v>
+      </c>
+      <c r="P11" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>1</v>
+      </c>
+      <c r="R11" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2492,7 +2601,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -3034,6 +3143,60 @@
         <v>0</v>
       </c>
       <c r="R10" s="3"/>
+    </row>
+    <row r="11" customFormat="1" ht="28" spans="1:18">
+      <c r="A11" s="9">
+        <v>917</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="3">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0</v>
+      </c>
+      <c r="K11" s="10">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N11" s="10">
+        <v>0</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0</v>
+      </c>
+      <c r="P11" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>0</v>
+      </c>
+      <c r="R11" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3044,7 +3207,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -3586,6 +3749,60 @@
         <v>5</v>
       </c>
       <c r="R10" s="3"/>
+    </row>
+    <row r="11" customFormat="1" ht="28" spans="1:18">
+      <c r="A11" s="11">
+        <v>917</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="3">
+        <v>34</v>
+      </c>
+      <c r="E11" s="3">
+        <v>12</v>
+      </c>
+      <c r="F11" s="3">
+        <v>4</v>
+      </c>
+      <c r="G11" s="3">
+        <v>3</v>
+      </c>
+      <c r="H11" s="3">
+        <v>3</v>
+      </c>
+      <c r="I11" s="3">
+        <v>5</v>
+      </c>
+      <c r="J11" s="3">
+        <v>5</v>
+      </c>
+      <c r="K11" s="10">
+        <v>0.1176</v>
+      </c>
+      <c r="L11" s="10">
+        <v>1.25</v>
+      </c>
+      <c r="M11" s="10">
+        <v>1</v>
+      </c>
+      <c r="N11" s="10">
+        <v>0.1471</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0</v>
+      </c>
+      <c r="P11" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>5</v>
+      </c>
+      <c r="R11" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12640" activeTab="3"/>
+    <workbookView windowWidth="29400" windowHeight="12640"/>
   </bookViews>
   <sheets>
     <sheet name="校边店海报1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="34">
   <si>
     <t>日期</t>
   </si>
@@ -1378,7 +1378,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:19">
@@ -1985,6 +1985,61 @@
       </c>
       <c r="R11" s="3"/>
       <c r="S11" s="9"/>
+    </row>
+    <row r="12" customFormat="1" ht="28" spans="1:19">
+      <c r="A12" s="9">
+        <v>918</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="3">
+        <v>39</v>
+      </c>
+      <c r="E12" s="3">
+        <v>12</v>
+      </c>
+      <c r="F12" s="3">
+        <v>6</v>
+      </c>
+      <c r="G12" s="3">
+        <v>4</v>
+      </c>
+      <c r="H12" s="3">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3">
+        <v>3</v>
+      </c>
+      <c r="K12" s="10">
+        <v>0.1538</v>
+      </c>
+      <c r="L12" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="M12" s="10">
+        <v>1</v>
+      </c>
+      <c r="N12" s="10">
+        <v>0.0769</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+      <c r="S12" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1995,7 +2050,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -2591,6 +2646,60 @@
         <v>1</v>
       </c>
       <c r="R11" s="3"/>
+    </row>
+    <row r="12" customFormat="1" ht="28" spans="1:18">
+      <c r="A12" s="11">
+        <v>918</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="3">
+        <v>9</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>2</v>
+      </c>
+      <c r="G12" s="3">
+        <v>2</v>
+      </c>
+      <c r="H12" s="3">
+        <v>2</v>
+      </c>
+      <c r="I12" s="3">
+        <v>2</v>
+      </c>
+      <c r="J12" s="3">
+        <v>2</v>
+      </c>
+      <c r="K12" s="10">
+        <v>0.2222</v>
+      </c>
+      <c r="L12" s="3">
+        <v>1</v>
+      </c>
+      <c r="M12" s="3">
+        <v>1</v>
+      </c>
+      <c r="N12" s="10">
+        <v>0.2222</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>2</v>
+      </c>
+      <c r="R12" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2601,7 +2710,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -3197,6 +3306,60 @@
         <v>0</v>
       </c>
       <c r="R11" s="3"/>
+    </row>
+    <row r="12" customFormat="1" ht="28" spans="1:18">
+      <c r="A12" s="9">
+        <v>918</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="3">
+        <v>7</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="10">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N12" s="10">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0</v>
+      </c>
+      <c r="R12" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3207,7 +3370,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -3803,6 +3966,60 @@
         <v>5</v>
       </c>
       <c r="R11" s="3"/>
+    </row>
+    <row r="12" customFormat="1" ht="28" spans="1:18">
+      <c r="A12" s="11">
+        <v>918</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="3">
+        <v>36</v>
+      </c>
+      <c r="E12" s="3">
+        <v>12</v>
+      </c>
+      <c r="F12" s="3">
+        <v>4</v>
+      </c>
+      <c r="G12" s="3">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3">
+        <v>5</v>
+      </c>
+      <c r="J12" s="3">
+        <v>5</v>
+      </c>
+      <c r="K12" s="10">
+        <v>0.1111</v>
+      </c>
+      <c r="L12" s="10">
+        <v>1.25</v>
+      </c>
+      <c r="M12" s="10">
+        <v>1</v>
+      </c>
+      <c r="N12" s="10">
+        <v>0.1389</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3813,8 +4030,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q8"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="7"/>
+  <dimension ref="A1:Q9"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="10.7692307692308"/>
     <col min="4" max="4" width="15.2307692307692" customWidth="1"/>
@@ -4100,6 +4317,41 @@
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
     </row>
+    <row r="9" ht="28" spans="1:17">
+      <c r="A9" s="3">
+        <v>1154362887</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="4">
+        <v>46282.7298611111</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
@@ -4109,6 +4361,7 @@
     <hyperlink ref="E6" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
     <hyperlink ref="E7" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
     <hyperlink ref="E8" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
+    <hyperlink ref="E9" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="34">
   <si>
     <t>日期</t>
   </si>
@@ -145,7 +145,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,6 +163,13 @@
     <font>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -686,137 +693,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -852,6 +859,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1378,7 +1388,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:19">
@@ -2040,6 +2050,61 @@
       </c>
       <c r="R12" s="3"/>
       <c r="S12" s="9"/>
+    </row>
+    <row r="13" customFormat="1" ht="28" spans="1:19">
+      <c r="A13" s="9">
+        <v>920</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="3">
+        <v>45</v>
+      </c>
+      <c r="E13" s="3">
+        <v>13</v>
+      </c>
+      <c r="F13" s="3">
+        <v>7</v>
+      </c>
+      <c r="G13" s="3">
+        <v>4</v>
+      </c>
+      <c r="H13" s="3">
+        <v>3</v>
+      </c>
+      <c r="I13" s="3">
+        <v>3</v>
+      </c>
+      <c r="J13" s="3">
+        <v>3</v>
+      </c>
+      <c r="K13" s="10">
+        <v>0.1556</v>
+      </c>
+      <c r="L13" s="10">
+        <v>0.4286</v>
+      </c>
+      <c r="M13" s="10">
+        <v>1</v>
+      </c>
+      <c r="N13" s="10">
+        <v>0.0667</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>3</v>
+      </c>
+      <c r="R13" s="3"/>
+      <c r="S13" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2050,7 +2115,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -2700,6 +2765,63 @@
         <v>2</v>
       </c>
       <c r="R12" s="3"/>
+    </row>
+    <row r="13" customFormat="1" ht="28" spans="1:18">
+      <c r="A13" s="11">
+        <v>920</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="3">
+        <v>10</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2</v>
+      </c>
+      <c r="F13" s="3">
+        <v>2</v>
+      </c>
+      <c r="G13" s="3">
+        <v>2</v>
+      </c>
+      <c r="H13" s="3">
+        <v>2</v>
+      </c>
+      <c r="I13" s="3">
+        <v>2</v>
+      </c>
+      <c r="J13" s="3">
+        <v>2</v>
+      </c>
+      <c r="K13" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="L13" s="3">
+        <v>1</v>
+      </c>
+      <c r="M13" s="3">
+        <v>1</v>
+      </c>
+      <c r="N13" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>2</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="D14" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2710,7 +2832,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -3360,6 +3482,60 @@
         <v>0</v>
       </c>
       <c r="R12" s="3"/>
+    </row>
+    <row r="13" customFormat="1" ht="28" spans="1:18">
+      <c r="A13" s="9">
+        <v>920</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="3">
+        <v>7</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0</v>
+      </c>
+      <c r="K13" s="10">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N13" s="10">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3370,7 +3546,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -4020,6 +4196,60 @@
         <v>5</v>
       </c>
       <c r="R12" s="3"/>
+    </row>
+    <row r="13" customFormat="1" ht="28" spans="1:18">
+      <c r="A13" s="11">
+        <v>920</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="3">
+        <v>37</v>
+      </c>
+      <c r="E13" s="3">
+        <v>12</v>
+      </c>
+      <c r="F13" s="3">
+        <v>4</v>
+      </c>
+      <c r="G13" s="3">
+        <v>3</v>
+      </c>
+      <c r="H13" s="3">
+        <v>3</v>
+      </c>
+      <c r="I13" s="3">
+        <v>5</v>
+      </c>
+      <c r="J13" s="3">
+        <v>5</v>
+      </c>
+      <c r="K13" s="10">
+        <v>0.1081</v>
+      </c>
+      <c r="L13" s="10">
+        <v>1.25</v>
+      </c>
+      <c r="M13" s="10">
+        <v>1</v>
+      </c>
+      <c r="N13" s="10">
+        <v>0.1351</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>5</v>
+      </c>
+      <c r="R13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12640"/>
+    <workbookView windowWidth="29400" windowHeight="12640" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="校边店海报1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="34">
   <si>
     <t>日期</t>
   </si>
@@ -1388,7 +1388,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:19">
@@ -2105,6 +2105,61 @@
       </c>
       <c r="R13" s="3"/>
       <c r="S13" s="9"/>
+    </row>
+    <row r="14" customFormat="1" ht="28" spans="1:19">
+      <c r="A14" s="9">
+        <v>921</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="3">
+        <v>46</v>
+      </c>
+      <c r="E14" s="3">
+        <v>13</v>
+      </c>
+      <c r="F14" s="3">
+        <v>7</v>
+      </c>
+      <c r="G14" s="3">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
+        <v>3</v>
+      </c>
+      <c r="K14" s="10">
+        <v>0.1522</v>
+      </c>
+      <c r="L14" s="10">
+        <v>0.4286</v>
+      </c>
+      <c r="M14" s="10">
+        <v>1</v>
+      </c>
+      <c r="N14" s="10">
+        <v>0.0652</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3"/>
+      <c r="S14" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2115,7 +2170,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -2820,8 +2875,62 @@
       </c>
       <c r="R13" s="3"/>
     </row>
-    <row r="14" spans="1:18">
-      <c r="D14" s="12"/>
+    <row r="14" customFormat="1" ht="28" spans="1:18">
+      <c r="A14" s="11">
+        <v>921</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="3">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>2</v>
+      </c>
+      <c r="G14" s="3">
+        <v>2</v>
+      </c>
+      <c r="H14" s="3">
+        <v>2</v>
+      </c>
+      <c r="I14" s="3">
+        <v>2</v>
+      </c>
+      <c r="J14" s="3">
+        <v>2</v>
+      </c>
+      <c r="K14" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="L14" s="3">
+        <v>1</v>
+      </c>
+      <c r="M14" s="3">
+        <v>1</v>
+      </c>
+      <c r="N14" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>2</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="D15" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2832,7 +2941,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -3536,6 +3645,63 @@
         <v>0</v>
       </c>
       <c r="R13" s="3"/>
+    </row>
+    <row r="14" customFormat="1" ht="28" spans="1:18">
+      <c r="A14" s="9">
+        <v>921</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="3">
+        <v>7</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="10">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N14" s="10">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="B15" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3546,7 +3712,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -4250,6 +4416,60 @@
         <v>5</v>
       </c>
       <c r="R13" s="3"/>
+    </row>
+    <row r="14" customFormat="1" ht="28" spans="1:18">
+      <c r="A14" s="11">
+        <v>921</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="3">
+        <v>38</v>
+      </c>
+      <c r="E14" s="3">
+        <v>12</v>
+      </c>
+      <c r="F14" s="3">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
+        <v>5</v>
+      </c>
+      <c r="K14" s="10">
+        <v>0.1053</v>
+      </c>
+      <c r="L14" s="10">
+        <v>1.25</v>
+      </c>
+      <c r="M14" s="10">
+        <v>1</v>
+      </c>
+      <c r="N14" s="10">
+        <v>0.1316</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12640" activeTab="4"/>
+    <workbookView windowWidth="29400" windowHeight="12640"/>
   </bookViews>
   <sheets>
     <sheet name="校边店海报1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="34">
   <si>
     <t>日期</t>
   </si>
@@ -145,7 +145,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,13 +163,6 @@
     <font>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -693,137 +686,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -859,9 +852,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1388,7 +1378,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:19">
@@ -2160,6 +2150,61 @@
       </c>
       <c r="R14" s="3"/>
       <c r="S14" s="9"/>
+    </row>
+    <row r="15" customFormat="1" ht="28" spans="1:19">
+      <c r="A15" s="9">
+        <v>922</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="3">
+        <v>47</v>
+      </c>
+      <c r="E15" s="3">
+        <v>13</v>
+      </c>
+      <c r="F15" s="3">
+        <v>7</v>
+      </c>
+      <c r="G15" s="3">
+        <v>4</v>
+      </c>
+      <c r="H15" s="3">
+        <v>3</v>
+      </c>
+      <c r="I15" s="3">
+        <v>3</v>
+      </c>
+      <c r="J15" s="3">
+        <v>3</v>
+      </c>
+      <c r="K15" s="10">
+        <v>0.1489</v>
+      </c>
+      <c r="L15" s="10">
+        <v>0.4286</v>
+      </c>
+      <c r="M15" s="10">
+        <v>1</v>
+      </c>
+      <c r="N15" s="10">
+        <v>0.0638</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3"/>
+      <c r="S15" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2929,8 +2974,59 @@
       </c>
       <c r="R14" s="3"/>
     </row>
-    <row r="15" spans="1:18">
-      <c r="D15" s="12"/>
+    <row r="15" customFormat="1" ht="28" spans="1:18">
+      <c r="A15" s="11">
+        <v>922</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="3">
+        <v>10</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>2</v>
+      </c>
+      <c r="G15" s="3">
+        <v>2</v>
+      </c>
+      <c r="H15" s="3">
+        <v>2</v>
+      </c>
+      <c r="I15" s="3">
+        <v>2</v>
+      </c>
+      <c r="J15" s="3">
+        <v>2</v>
+      </c>
+      <c r="K15" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="L15" s="3">
+        <v>1</v>
+      </c>
+      <c r="M15" s="3">
+        <v>1</v>
+      </c>
+      <c r="N15" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>2</v>
+      </c>
+      <c r="R15" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3700,8 +3796,59 @@
       </c>
       <c r="R14" s="3"/>
     </row>
-    <row r="15" spans="1:18">
-      <c r="B15" s="12"/>
+    <row r="15" customFormat="1" ht="28" spans="1:18">
+      <c r="A15" s="9">
+        <v>922</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="3">
+        <v>7</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="10">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N15" s="10">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3712,7 +3859,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -4470,6 +4617,60 @@
         <v>5</v>
       </c>
       <c r="R14" s="3"/>
+    </row>
+    <row r="15" customFormat="1" ht="28" spans="1:18">
+      <c r="A15" s="11">
+        <v>922</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="3">
+        <v>39</v>
+      </c>
+      <c r="E15" s="3">
+        <v>12</v>
+      </c>
+      <c r="F15" s="3">
+        <v>4</v>
+      </c>
+      <c r="G15" s="3">
+        <v>3</v>
+      </c>
+      <c r="H15" s="3">
+        <v>3</v>
+      </c>
+      <c r="I15" s="3">
+        <v>5</v>
+      </c>
+      <c r="J15" s="3">
+        <v>5</v>
+      </c>
+      <c r="K15" s="10">
+        <v>0.1026</v>
+      </c>
+      <c r="L15" s="10">
+        <v>1.25</v>
+      </c>
+      <c r="M15" s="10">
+        <v>1</v>
+      </c>
+      <c r="N15" s="10">
+        <v>0.1282</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>5</v>
+      </c>
+      <c r="R15" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12640"/>
+    <workbookView windowWidth="29400" windowHeight="12640" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="校边店海报1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="34">
   <si>
     <t>日期</t>
   </si>
@@ -1378,7 +1378,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:19">
@@ -2205,6 +2205,61 @@
       </c>
       <c r="R15" s="3"/>
       <c r="S15" s="9"/>
+    </row>
+    <row r="16" customFormat="1" ht="28" spans="1:19">
+      <c r="A16" s="9">
+        <v>923</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="3">
+        <v>52</v>
+      </c>
+      <c r="E16" s="3">
+        <v>14</v>
+      </c>
+      <c r="F16" s="3">
+        <v>7</v>
+      </c>
+      <c r="G16" s="3">
+        <v>4</v>
+      </c>
+      <c r="H16" s="3">
+        <v>3</v>
+      </c>
+      <c r="I16" s="3">
+        <v>4</v>
+      </c>
+      <c r="J16" s="3">
+        <v>4</v>
+      </c>
+      <c r="K16" s="10">
+        <v>0.1346</v>
+      </c>
+      <c r="L16" s="10">
+        <v>0.5714</v>
+      </c>
+      <c r="M16" s="10">
+        <v>1</v>
+      </c>
+      <c r="N16" s="10">
+        <v>0.0769</v>
+      </c>
+      <c r="O16" s="3">
+        <v>0</v>
+      </c>
+      <c r="P16" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>4</v>
+      </c>
+      <c r="R16" s="3"/>
+      <c r="S16" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2215,7 +2270,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -3027,6 +3082,60 @@
         <v>2</v>
       </c>
       <c r="R15" s="3"/>
+    </row>
+    <row r="16" customFormat="1" ht="28" spans="1:18">
+      <c r="A16" s="11">
+        <v>923</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="3">
+        <v>10</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>2</v>
+      </c>
+      <c r="G16" s="3">
+        <v>2</v>
+      </c>
+      <c r="H16" s="3">
+        <v>2</v>
+      </c>
+      <c r="I16" s="3">
+        <v>2</v>
+      </c>
+      <c r="J16" s="3">
+        <v>2</v>
+      </c>
+      <c r="K16" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="L16" s="3">
+        <v>1</v>
+      </c>
+      <c r="M16" s="3">
+        <v>1</v>
+      </c>
+      <c r="N16" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="O16" s="3">
+        <v>0</v>
+      </c>
+      <c r="P16" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>2</v>
+      </c>
+      <c r="R16" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3037,10 +3146,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
-    <row r="1" ht="28" spans="1:18">
+    <row r="1" ht="28" spans="1:19">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3094,7 +3203,7 @@
       </c>
       <c r="R1" s="8"/>
     </row>
-    <row r="2" ht="28" spans="1:18">
+    <row r="2" ht="28" spans="1:19">
       <c r="A2" s="11">
         <v>904</v>
       </c>
@@ -3148,7 +3257,7 @@
       </c>
       <c r="R2" s="3"/>
     </row>
-    <row r="3" customFormat="1" ht="28" spans="1:18">
+    <row r="3" customFormat="1" ht="28" spans="1:19">
       <c r="A3" s="11">
         <v>907</v>
       </c>
@@ -3202,7 +3311,7 @@
       </c>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" ht="28" spans="1:18">
+    <row r="4" ht="28" spans="1:19">
       <c r="A4" s="11">
         <v>908</v>
       </c>
@@ -3256,7 +3365,7 @@
       </c>
       <c r="R4" s="3"/>
     </row>
-    <row r="5" ht="28" spans="1:18">
+    <row r="5" ht="28" spans="1:19">
       <c r="A5" s="9">
         <v>909</v>
       </c>
@@ -3310,7 +3419,7 @@
       </c>
       <c r="R5" s="3"/>
     </row>
-    <row r="6" customFormat="1" ht="28" spans="1:18">
+    <row r="6" customFormat="1" ht="28" spans="1:19">
       <c r="A6" s="9">
         <v>910</v>
       </c>
@@ -3364,7 +3473,7 @@
       </c>
       <c r="R6" s="3"/>
     </row>
-    <row r="7" customFormat="1" ht="28" spans="1:18">
+    <row r="7" customFormat="1" ht="28" spans="1:19">
       <c r="A7" s="9">
         <v>911</v>
       </c>
@@ -3418,7 +3527,7 @@
       </c>
       <c r="R7" s="3"/>
     </row>
-    <row r="8" customFormat="1" ht="28" spans="1:18">
+    <row r="8" customFormat="1" ht="28" spans="1:19">
       <c r="A8" s="9">
         <v>914</v>
       </c>
@@ -3472,7 +3581,7 @@
       </c>
       <c r="R8" s="3"/>
     </row>
-    <row r="9" customFormat="1" ht="28" spans="1:18">
+    <row r="9" customFormat="1" ht="28" spans="1:19">
       <c r="A9" s="9">
         <v>915</v>
       </c>
@@ -3526,7 +3635,7 @@
       </c>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" customFormat="1" ht="28" spans="1:18">
+    <row r="10" customFormat="1" ht="28" spans="1:19">
       <c r="A10" s="9">
         <v>916</v>
       </c>
@@ -3580,7 +3689,7 @@
       </c>
       <c r="R10" s="3"/>
     </row>
-    <row r="11" customFormat="1" ht="28" spans="1:18">
+    <row r="11" customFormat="1" ht="28" spans="1:19">
       <c r="A11" s="9">
         <v>917</v>
       </c>
@@ -3634,7 +3743,7 @@
       </c>
       <c r="R11" s="3"/>
     </row>
-    <row r="12" customFormat="1" ht="28" spans="1:18">
+    <row r="12" customFormat="1" ht="28" spans="1:19">
       <c r="A12" s="9">
         <v>918</v>
       </c>
@@ -3688,7 +3797,7 @@
       </c>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" customFormat="1" ht="28" spans="1:18">
+    <row r="13" customFormat="1" ht="28" spans="1:19">
       <c r="A13" s="9">
         <v>920</v>
       </c>
@@ -3742,7 +3851,7 @@
       </c>
       <c r="R13" s="3"/>
     </row>
-    <row r="14" customFormat="1" ht="28" spans="1:18">
+    <row r="14" customFormat="1" ht="28" spans="1:19">
       <c r="A14" s="9">
         <v>921</v>
       </c>
@@ -3796,7 +3905,7 @@
       </c>
       <c r="R14" s="3"/>
     </row>
-    <row r="15" customFormat="1" ht="28" spans="1:18">
+    <row r="15" customFormat="1" ht="28" spans="1:19">
       <c r="A15" s="9">
         <v>922</v>
       </c>
@@ -3849,6 +3958,65 @@
         <v>0</v>
       </c>
       <c r="R15" s="3"/>
+    </row>
+    <row r="16" customFormat="1" ht="28" spans="1:19">
+      <c r="A16" s="9">
+        <v>923</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="3">
+        <v>7</v>
+      </c>
+      <c r="G16" s="3">
+        <v>2</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0</v>
+      </c>
+      <c r="K16" s="10">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0</v>
+      </c>
+      <c r="N16" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P16" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>0</v>
+      </c>
+      <c r="R16" s="3">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3859,7 +4027,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -4671,6 +4839,60 @@
         <v>5</v>
       </c>
       <c r="R15" s="3"/>
+    </row>
+    <row r="16" customFormat="1" ht="28" spans="1:18">
+      <c r="A16" s="11">
+        <v>923</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="3">
+        <v>39</v>
+      </c>
+      <c r="E16" s="3">
+        <v>12</v>
+      </c>
+      <c r="F16" s="3">
+        <v>4</v>
+      </c>
+      <c r="G16" s="3">
+        <v>3</v>
+      </c>
+      <c r="H16" s="3">
+        <v>3</v>
+      </c>
+      <c r="I16" s="3">
+        <v>5</v>
+      </c>
+      <c r="J16" s="3">
+        <v>5</v>
+      </c>
+      <c r="K16" s="10">
+        <v>0.1026</v>
+      </c>
+      <c r="L16" s="10">
+        <v>1.25</v>
+      </c>
+      <c r="M16" s="10">
+        <v>1</v>
+      </c>
+      <c r="N16" s="10">
+        <v>0.1282</v>
+      </c>
+      <c r="O16" s="3">
+        <v>0</v>
+      </c>
+      <c r="P16" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>5</v>
+      </c>
+      <c r="R16" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4681,7 +4903,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="10.7692307692308"/>
@@ -5002,6 +5224,41 @@
       <c r="O9" s="5"/>
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
+    </row>
+    <row r="10" ht="28" spans="1:17">
+      <c r="A10" s="3">
+        <v>289648316</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="4">
+        <v>46287.8625</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5013,6 +5270,7 @@
     <hyperlink ref="E7" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
     <hyperlink ref="E8" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
     <hyperlink ref="E9" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
+    <hyperlink ref="E10" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12640" activeTab="4"/>
+    <workbookView windowWidth="29400" windowHeight="12640" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="校边店海报1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="34">
   <si>
     <t>日期</t>
   </si>
@@ -3146,10 +3146,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
-    <row r="1" ht="28" spans="1:19">
+    <row r="1" ht="28" spans="1:18">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="R1" s="8"/>
     </row>
-    <row r="2" ht="28" spans="1:19">
+    <row r="2" ht="28" spans="1:18">
       <c r="A2" s="11">
         <v>904</v>
       </c>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="R2" s="3"/>
     </row>
-    <row r="3" customFormat="1" ht="28" spans="1:19">
+    <row r="3" customFormat="1" ht="28" spans="1:18">
       <c r="A3" s="11">
         <v>907</v>
       </c>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" ht="28" spans="1:19">
+    <row r="4" ht="28" spans="1:18">
       <c r="A4" s="11">
         <v>908</v>
       </c>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="R4" s="3"/>
     </row>
-    <row r="5" ht="28" spans="1:19">
+    <row r="5" ht="28" spans="1:18">
       <c r="A5" s="9">
         <v>909</v>
       </c>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="R5" s="3"/>
     </row>
-    <row r="6" customFormat="1" ht="28" spans="1:19">
+    <row r="6" customFormat="1" ht="28" spans="1:18">
       <c r="A6" s="9">
         <v>910</v>
       </c>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="R6" s="3"/>
     </row>
-    <row r="7" customFormat="1" ht="28" spans="1:19">
+    <row r="7" customFormat="1" ht="28" spans="1:18">
       <c r="A7" s="9">
         <v>911</v>
       </c>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="R7" s="3"/>
     </row>
-    <row r="8" customFormat="1" ht="28" spans="1:19">
+    <row r="8" customFormat="1" ht="28" spans="1:18">
       <c r="A8" s="9">
         <v>914</v>
       </c>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="R8" s="3"/>
     </row>
-    <row r="9" customFormat="1" ht="28" spans="1:19">
+    <row r="9" customFormat="1" ht="28" spans="1:18">
       <c r="A9" s="9">
         <v>915</v>
       </c>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" customFormat="1" ht="28" spans="1:19">
+    <row r="10" customFormat="1" ht="28" spans="1:18">
       <c r="A10" s="9">
         <v>916</v>
       </c>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="R10" s="3"/>
     </row>
-    <row r="11" customFormat="1" ht="28" spans="1:19">
+    <row r="11" customFormat="1" ht="28" spans="1:18">
       <c r="A11" s="9">
         <v>917</v>
       </c>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="R11" s="3"/>
     </row>
-    <row r="12" customFormat="1" ht="28" spans="1:19">
+    <row r="12" customFormat="1" ht="28" spans="1:18">
       <c r="A12" s="9">
         <v>918</v>
       </c>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" customFormat="1" ht="28" spans="1:19">
+    <row r="13" customFormat="1" ht="28" spans="1:18">
       <c r="A13" s="9">
         <v>920</v>
       </c>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="R13" s="3"/>
     </row>
-    <row r="14" customFormat="1" ht="28" spans="1:19">
+    <row r="14" customFormat="1" ht="28" spans="1:18">
       <c r="A14" s="9">
         <v>921</v>
       </c>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="R14" s="3"/>
     </row>
-    <row r="15" customFormat="1" ht="28" spans="1:19">
+    <row r="15" customFormat="1" ht="28" spans="1:18">
       <c r="A15" s="9">
         <v>922</v>
       </c>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" customFormat="1" ht="28" spans="1:19">
+    <row r="16" customFormat="1" ht="28" spans="1:18">
       <c r="A16" s="9">
         <v>923</v>
       </c>
@@ -3969,17 +3969,17 @@
       <c r="C16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>18</v>
+      <c r="D16" s="3">
+        <v>7</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2</v>
       </c>
       <c r="F16" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G16" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H16" s="3">
         <v>0</v>
@@ -3993,18 +3993,18 @@
       <c r="K16" s="10">
         <v>0</v>
       </c>
-      <c r="L16" s="3">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3">
-        <v>0</v>
-      </c>
-      <c r="N16" s="10" t="s">
+      <c r="L16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O16" s="3" t="s">
+      <c r="M16" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="N16" s="10">
+        <v>0</v>
+      </c>
+      <c r="O16" s="3">
+        <v>0</v>
+      </c>
       <c r="P16" s="3">
         <v>0</v>
       </c>
@@ -4012,9 +4012,6 @@
         <v>0</v>
       </c>
       <c r="R16" s="3">
-        <v>0</v>
-      </c>
-      <c r="S16">
         <v>0</v>
       </c>
     </row>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12640" activeTab="2"/>
+    <workbookView windowWidth="29400" windowHeight="12640" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="校边店海报1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="34">
   <si>
     <t>日期</t>
   </si>
@@ -1378,7 +1378,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:19">
@@ -2260,6 +2260,61 @@
       </c>
       <c r="R16" s="3"/>
       <c r="S16" s="9"/>
+    </row>
+    <row r="17" customFormat="1" ht="28" spans="1:19">
+      <c r="A17" s="9">
+        <v>924</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="3">
+        <v>60</v>
+      </c>
+      <c r="E17" s="3">
+        <v>16</v>
+      </c>
+      <c r="F17" s="3">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3">
+        <v>4</v>
+      </c>
+      <c r="H17" s="3">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3">
+        <v>5</v>
+      </c>
+      <c r="K17" s="10">
+        <v>0.1333</v>
+      </c>
+      <c r="L17" s="10">
+        <v>0.625</v>
+      </c>
+      <c r="M17" s="10">
+        <v>1</v>
+      </c>
+      <c r="N17" s="10">
+        <v>0.0833</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3"/>
+      <c r="S17" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2270,7 +2325,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -3136,6 +3191,60 @@
         <v>2</v>
       </c>
       <c r="R16" s="3"/>
+    </row>
+    <row r="17" customFormat="1" ht="28" spans="1:18">
+      <c r="A17" s="11">
+        <v>924</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="3">
+        <v>10</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2</v>
+      </c>
+      <c r="G17" s="3">
+        <v>2</v>
+      </c>
+      <c r="H17" s="3">
+        <v>2</v>
+      </c>
+      <c r="I17" s="3">
+        <v>2</v>
+      </c>
+      <c r="J17" s="3">
+        <v>2</v>
+      </c>
+      <c r="K17" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="L17" s="3">
+        <v>1</v>
+      </c>
+      <c r="M17" s="3">
+        <v>1</v>
+      </c>
+      <c r="N17" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>2</v>
+      </c>
+      <c r="R17" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3146,7 +3255,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -4011,9 +4120,61 @@
       <c r="Q16" s="3">
         <v>0</v>
       </c>
-      <c r="R16" s="3">
-        <v>0</v>
-      </c>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" customFormat="1" ht="28" spans="1:18">
+      <c r="A17" s="9">
+        <v>924</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="3">
+        <v>7</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0</v>
+      </c>
+      <c r="K17" s="10">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N17" s="10">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>0</v>
+      </c>
+      <c r="R17" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4024,7 +4185,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -4890,6 +5051,60 @@
         <v>5</v>
       </c>
       <c r="R16" s="3"/>
+    </row>
+    <row r="17" customFormat="1" ht="28" spans="1:18">
+      <c r="A17" s="11">
+        <v>924</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="3">
+        <v>40</v>
+      </c>
+      <c r="E17" s="3">
+        <v>12</v>
+      </c>
+      <c r="F17" s="3">
+        <v>4</v>
+      </c>
+      <c r="G17" s="3">
+        <v>3</v>
+      </c>
+      <c r="H17" s="3">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3">
+        <v>5</v>
+      </c>
+      <c r="K17" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="L17" s="10">
+        <v>1.25</v>
+      </c>
+      <c r="M17" s="10">
+        <v>1</v>
+      </c>
+      <c r="N17" s="10">
+        <v>0.125</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12640" activeTab="3"/>
+    <workbookView windowWidth="29400" windowHeight="12620"/>
   </bookViews>
   <sheets>
     <sheet name="校边店海报1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="34">
   <si>
     <t>日期</t>
   </si>
@@ -1378,7 +1378,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:19">
@@ -2315,6 +2315,61 @@
       </c>
       <c r="R17" s="3"/>
       <c r="S17" s="9"/>
+    </row>
+    <row r="18" customFormat="1" ht="28" spans="1:19">
+      <c r="A18" s="9">
+        <v>928</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="3">
+        <v>74</v>
+      </c>
+      <c r="E18" s="3">
+        <v>21</v>
+      </c>
+      <c r="F18" s="3">
+        <v>12</v>
+      </c>
+      <c r="G18" s="3">
+        <v>6</v>
+      </c>
+      <c r="H18" s="3">
+        <v>5</v>
+      </c>
+      <c r="I18" s="3">
+        <v>7</v>
+      </c>
+      <c r="J18" s="3">
+        <v>7</v>
+      </c>
+      <c r="K18" s="10">
+        <v>0.1622</v>
+      </c>
+      <c r="L18" s="10">
+        <v>0.5833</v>
+      </c>
+      <c r="M18" s="10">
+        <v>1</v>
+      </c>
+      <c r="N18" s="10">
+        <v>0.0946</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>7</v>
+      </c>
+      <c r="R18" s="3"/>
+      <c r="S18" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2325,7 +2380,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -3245,6 +3300,60 @@
         <v>2</v>
       </c>
       <c r="R17" s="3"/>
+    </row>
+    <row r="18" customFormat="1" ht="28" spans="1:18">
+      <c r="A18" s="11">
+        <v>928</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="3">
+        <v>11</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2</v>
+      </c>
+      <c r="F18" s="3">
+        <v>2</v>
+      </c>
+      <c r="G18" s="3">
+        <v>2</v>
+      </c>
+      <c r="H18" s="3">
+        <v>2</v>
+      </c>
+      <c r="I18" s="3">
+        <v>2</v>
+      </c>
+      <c r="J18" s="3">
+        <v>2</v>
+      </c>
+      <c r="K18" s="10">
+        <v>0.1818</v>
+      </c>
+      <c r="L18" s="3">
+        <v>1</v>
+      </c>
+      <c r="M18" s="3">
+        <v>1</v>
+      </c>
+      <c r="N18" s="10">
+        <v>0.1818</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>2</v>
+      </c>
+      <c r="R18" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3255,7 +3364,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -4175,6 +4284,60 @@
         <v>0</v>
       </c>
       <c r="R17" s="3"/>
+    </row>
+    <row r="18" customFormat="1" ht="28" spans="1:18">
+      <c r="A18" s="9">
+        <v>928</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="3">
+        <v>7</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="10">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N18" s="10">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>0</v>
+      </c>
+      <c r="R18" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4185,7 +4348,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -4998,7 +5161,7 @@
       </c>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" customFormat="1" ht="28" spans="1:18">
+    <row r="16" customFormat="1" ht="27" customHeight="1" spans="1:18">
       <c r="A16" s="11">
         <v>923</v>
       </c>
@@ -5105,6 +5268,60 @@
         <v>5</v>
       </c>
       <c r="R17" s="3"/>
+    </row>
+    <row r="18" customFormat="1" ht="28" spans="1:18">
+      <c r="A18" s="11">
+        <v>928</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="3">
+        <v>46</v>
+      </c>
+      <c r="E18" s="3">
+        <v>14</v>
+      </c>
+      <c r="F18" s="3">
+        <v>6</v>
+      </c>
+      <c r="G18" s="3">
+        <v>4</v>
+      </c>
+      <c r="H18" s="3">
+        <v>4</v>
+      </c>
+      <c r="I18" s="3">
+        <v>6</v>
+      </c>
+      <c r="J18" s="3">
+        <v>6</v>
+      </c>
+      <c r="K18" s="10">
+        <v>0.1304</v>
+      </c>
+      <c r="L18" s="10">
+        <v>1</v>
+      </c>
+      <c r="M18" s="10">
+        <v>1</v>
+      </c>
+      <c r="N18" s="10">
+        <v>0.1304</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>6</v>
+      </c>
+      <c r="R18" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5115,7 +5332,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="10.7692307692308"/>
@@ -5471,6 +5688,76 @@
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
+    </row>
+    <row r="11" ht="28" spans="1:17">
+      <c r="A11" s="3">
+        <v>656893871</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="4">
+        <v>46290.4326388889</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+    </row>
+    <row r="12" ht="28" spans="1:17">
+      <c r="A12" s="3">
+        <v>43515675</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="4">
+        <v>46289.7576388889</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5483,6 +5770,8 @@
     <hyperlink ref="E8" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
     <hyperlink ref="E9" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
     <hyperlink ref="E10" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
+    <hyperlink ref="E11" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
+    <hyperlink ref="E12" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12620"/>
+    <workbookView windowWidth="29400" windowHeight="12620" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="校边店海报1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="34">
   <si>
     <t>日期</t>
   </si>
@@ -1378,7 +1378,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:19">
@@ -2370,6 +2370,61 @@
       </c>
       <c r="R18" s="3"/>
       <c r="S18" s="9"/>
+    </row>
+    <row r="19" customFormat="1" ht="28" spans="1:19">
+      <c r="A19" s="9">
+        <v>929</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="3">
+        <v>75</v>
+      </c>
+      <c r="E19" s="3">
+        <v>21</v>
+      </c>
+      <c r="F19" s="3">
+        <v>12</v>
+      </c>
+      <c r="G19" s="3">
+        <v>6</v>
+      </c>
+      <c r="H19" s="3">
+        <v>5</v>
+      </c>
+      <c r="I19" s="3">
+        <v>7</v>
+      </c>
+      <c r="J19" s="3">
+        <v>7</v>
+      </c>
+      <c r="K19" s="10">
+        <v>0.16</v>
+      </c>
+      <c r="L19" s="10">
+        <v>0.5833</v>
+      </c>
+      <c r="M19" s="10">
+        <v>1</v>
+      </c>
+      <c r="N19" s="10">
+        <v>0.0933</v>
+      </c>
+      <c r="O19" s="3">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>7</v>
+      </c>
+      <c r="R19" s="3"/>
+      <c r="S19" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2380,7 +2435,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -3354,6 +3409,60 @@
         <v>2</v>
       </c>
       <c r="R18" s="3"/>
+    </row>
+    <row r="19" customFormat="1" ht="28" spans="1:18">
+      <c r="A19" s="11">
+        <v>929</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="3">
+        <v>11</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2</v>
+      </c>
+      <c r="G19" s="3">
+        <v>2</v>
+      </c>
+      <c r="H19" s="3">
+        <v>2</v>
+      </c>
+      <c r="I19" s="3">
+        <v>2</v>
+      </c>
+      <c r="J19" s="3">
+        <v>2</v>
+      </c>
+      <c r="K19" s="10">
+        <v>0.1818</v>
+      </c>
+      <c r="L19" s="3">
+        <v>1</v>
+      </c>
+      <c r="M19" s="3">
+        <v>1</v>
+      </c>
+      <c r="N19" s="10">
+        <v>0.1818</v>
+      </c>
+      <c r="O19" s="3">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>2</v>
+      </c>
+      <c r="R19" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3364,7 +3473,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -4231,7 +4340,7 @@
       </c>
       <c r="R16" s="3"/>
     </row>
-    <row r="17" customFormat="1" ht="28" spans="1:18">
+    <row r="17" customFormat="1" ht="28" spans="1:19">
       <c r="A17" s="9">
         <v>924</v>
       </c>
@@ -4285,7 +4394,7 @@
       </c>
       <c r="R17" s="3"/>
     </row>
-    <row r="18" customFormat="1" ht="28" spans="1:18">
+    <row r="18" customFormat="1" ht="28" spans="1:19">
       <c r="A18" s="9">
         <v>928</v>
       </c>
@@ -4338,6 +4447,65 @@
         <v>0</v>
       </c>
       <c r="R18" s="3"/>
+    </row>
+    <row r="19" customFormat="1" ht="28" spans="1:19">
+      <c r="A19" s="9">
+        <v>929</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="3">
+        <v>7</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0</v>
+      </c>
+      <c r="K19" s="10">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N19" s="10">
+        <v>0</v>
+      </c>
+      <c r="O19" s="3">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>0</v>
+      </c>
+      <c r="R19" s="3">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4348,7 +4516,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -5322,6 +5490,60 @@
         <v>6</v>
       </c>
       <c r="R18" s="3"/>
+    </row>
+    <row r="19" customFormat="1" ht="28" spans="1:18">
+      <c r="A19" s="11">
+        <v>929</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="3">
+        <v>46</v>
+      </c>
+      <c r="E19" s="3">
+        <v>14</v>
+      </c>
+      <c r="F19" s="3">
+        <v>6</v>
+      </c>
+      <c r="G19" s="3">
+        <v>4</v>
+      </c>
+      <c r="H19" s="3">
+        <v>4</v>
+      </c>
+      <c r="I19" s="3">
+        <v>6</v>
+      </c>
+      <c r="J19" s="3">
+        <v>6</v>
+      </c>
+      <c r="K19" s="10">
+        <v>0.1304</v>
+      </c>
+      <c r="L19" s="10">
+        <v>1</v>
+      </c>
+      <c r="M19" s="10">
+        <v>1</v>
+      </c>
+      <c r="N19" s="10">
+        <v>0.1304</v>
+      </c>
+      <c r="O19" s="3">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>6</v>
+      </c>
+      <c r="R19" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="36">
   <si>
     <t>日期</t>
   </si>
@@ -133,6 +133,12 @@
   </si>
   <si>
     <t>已中奖</t>
+  </si>
+  <si>
+    <t>3103935-5宝石</t>
+  </si>
+  <si>
+    <t>5宝石</t>
   </si>
 </sst>
 </file>
@@ -1378,7 +1384,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:19">
@@ -2425,6 +2431,61 @@
       </c>
       <c r="R19" s="3"/>
       <c r="S19" s="9"/>
+    </row>
+    <row r="20" customFormat="1" ht="28" spans="1:19">
+      <c r="A20" s="9">
+        <v>930</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="3">
+        <v>86</v>
+      </c>
+      <c r="E20" s="3">
+        <v>24</v>
+      </c>
+      <c r="F20" s="3">
+        <v>14</v>
+      </c>
+      <c r="G20" s="3">
+        <v>7</v>
+      </c>
+      <c r="H20" s="3">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3">
+        <v>8</v>
+      </c>
+      <c r="K20" s="10">
+        <v>0.1628</v>
+      </c>
+      <c r="L20" s="10">
+        <v>0.5714</v>
+      </c>
+      <c r="M20" s="10">
+        <v>1</v>
+      </c>
+      <c r="N20" s="10">
+        <v>0.093</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3"/>
+      <c r="S20" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2435,7 +2496,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -3463,6 +3524,60 @@
         <v>2</v>
       </c>
       <c r="R19" s="3"/>
+    </row>
+    <row r="20" customFormat="1" ht="28" spans="1:18">
+      <c r="A20" s="11">
+        <v>930</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="3">
+        <v>12</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2</v>
+      </c>
+      <c r="F20" s="3">
+        <v>2</v>
+      </c>
+      <c r="G20" s="3">
+        <v>2</v>
+      </c>
+      <c r="H20" s="3">
+        <v>2</v>
+      </c>
+      <c r="I20" s="3">
+        <v>2</v>
+      </c>
+      <c r="J20" s="3">
+        <v>2</v>
+      </c>
+      <c r="K20" s="10">
+        <v>0.1667</v>
+      </c>
+      <c r="L20" s="3">
+        <v>1</v>
+      </c>
+      <c r="M20" s="3">
+        <v>1</v>
+      </c>
+      <c r="N20" s="10">
+        <v>0.1667</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>2</v>
+      </c>
+      <c r="R20" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3473,7 +3588,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -4506,6 +4621,60 @@
       <c r="S19">
         <v>0</v>
       </c>
+    </row>
+    <row r="20" customFormat="1" ht="28" spans="1:19">
+      <c r="A20" s="9">
+        <v>930</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="3">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="10">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N20" s="10">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4516,7 +4685,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -5544,6 +5713,60 @@
         <v>6</v>
       </c>
       <c r="R19" s="3"/>
+    </row>
+    <row r="20" customFormat="1" ht="28" spans="1:18">
+      <c r="A20" s="11">
+        <v>930</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="3">
+        <v>47</v>
+      </c>
+      <c r="E20" s="3">
+        <v>14</v>
+      </c>
+      <c r="F20" s="3">
+        <v>6</v>
+      </c>
+      <c r="G20" s="3">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3">
+        <v>6</v>
+      </c>
+      <c r="J20" s="3">
+        <v>6</v>
+      </c>
+      <c r="K20" s="10">
+        <v>0.1277</v>
+      </c>
+      <c r="L20" s="10">
+        <v>1</v>
+      </c>
+      <c r="M20" s="10">
+        <v>1</v>
+      </c>
+      <c r="N20" s="10">
+        <v>0.1277</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>6</v>
+      </c>
+      <c r="R20" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5554,7 +5777,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="10.7692307692308"/>
@@ -5980,6 +6203,39 @@
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
+    </row>
+    <row r="13" ht="28" spans="1:17">
+      <c r="A13" s="3">
+        <v>682484537</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="4">
+        <v>46294.8340277778</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5994,6 +6250,7 @@
     <hyperlink ref="E10" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
     <hyperlink ref="E11" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
     <hyperlink ref="E12" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
+    <hyperlink ref="E13" r:id="rId2" display="3103935-5宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103935"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12520" activeTab="4"/>
+    <workbookView windowWidth="29400" windowHeight="12520" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="校边店海报1" sheetId="1" r:id="rId1"/>
@@ -2489,7 +2489,7 @@
     </row>
     <row r="21" customFormat="1" ht="28" spans="1:19">
       <c r="A21" s="9">
-        <v>108</v>
+        <v>1008</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>17</v>
@@ -3635,8 +3635,8 @@
       <c r="R20" s="3"/>
     </row>
     <row r="21" customFormat="1" ht="28" spans="1:18">
-      <c r="A21" s="11">
-        <v>108</v>
+      <c r="A21" s="9">
+        <v>1008</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>17</v>
@@ -4782,7 +4782,7 @@
     </row>
     <row r="21" customFormat="1" ht="28" spans="1:18">
       <c r="A21" s="9">
-        <v>108</v>
+        <v>1008</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>17</v>
@@ -5928,7 +5928,7 @@
     </row>
     <row r="21" customFormat="1" ht="28" spans="1:18">
       <c r="A21" s="11">
-        <v>108</v>
+        <v>1008</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>17</v>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12520" activeTab="3"/>
+    <workbookView windowWidth="29400" windowHeight="12520"/>
   </bookViews>
   <sheets>
     <sheet name="校边店海报1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="36">
   <si>
     <t>日期</t>
   </si>
@@ -1384,7 +1384,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:19">
@@ -2541,6 +2541,61 @@
       </c>
       <c r="R21" s="3"/>
       <c r="S21" s="9"/>
+    </row>
+    <row r="22" customFormat="1" ht="28" spans="1:19">
+      <c r="A22" s="9">
+        <v>1009</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="3">
+        <v>112</v>
+      </c>
+      <c r="E22" s="3">
+        <v>31</v>
+      </c>
+      <c r="F22" s="3">
+        <v>18</v>
+      </c>
+      <c r="G22" s="3">
+        <v>7</v>
+      </c>
+      <c r="H22" s="3">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3">
+        <v>10</v>
+      </c>
+      <c r="J22" s="3">
+        <v>10</v>
+      </c>
+      <c r="K22" s="10">
+        <v>0.1607</v>
+      </c>
+      <c r="L22" s="10">
+        <v>0.5556</v>
+      </c>
+      <c r="M22" s="10">
+        <v>1</v>
+      </c>
+      <c r="N22" s="10">
+        <v>0.0893</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>10</v>
+      </c>
+      <c r="R22" s="3"/>
+      <c r="S22" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2551,7 +2606,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -3687,6 +3742,60 @@
         <v>3</v>
       </c>
       <c r="R21" s="3"/>
+    </row>
+    <row r="22" customFormat="1" ht="28" spans="1:18">
+      <c r="A22" s="9">
+        <v>1009</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="3">
+        <v>14</v>
+      </c>
+      <c r="E22" s="3">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3">
+        <v>2</v>
+      </c>
+      <c r="G22" s="3">
+        <v>2</v>
+      </c>
+      <c r="H22" s="3">
+        <v>2</v>
+      </c>
+      <c r="I22" s="3">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
+        <v>3</v>
+      </c>
+      <c r="K22" s="10">
+        <v>0.1429</v>
+      </c>
+      <c r="L22" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M22" s="3">
+        <v>1</v>
+      </c>
+      <c r="N22" s="10">
+        <v>0.2143</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3697,7 +3806,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -4833,6 +4942,60 @@
         <v>0</v>
       </c>
       <c r="R21" s="3"/>
+    </row>
+    <row r="22" customFormat="1" ht="28" spans="1:18">
+      <c r="A22" s="9">
+        <v>1009</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="3">
+        <v>9</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="10">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N22" s="10">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4843,7 +5006,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -5979,6 +6142,60 @@
         <v>6</v>
       </c>
       <c r="R21" s="3"/>
+    </row>
+    <row r="22" customFormat="1" ht="28" spans="1:18">
+      <c r="A22" s="11">
+        <v>1009</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="3">
+        <v>52</v>
+      </c>
+      <c r="E22" s="3">
+        <v>14</v>
+      </c>
+      <c r="F22" s="3">
+        <v>6</v>
+      </c>
+      <c r="G22" s="3">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3">
+        <v>6</v>
+      </c>
+      <c r="J22" s="3">
+        <v>6</v>
+      </c>
+      <c r="K22" s="10">
+        <v>0.1154</v>
+      </c>
+      <c r="L22" s="10">
+        <v>1</v>
+      </c>
+      <c r="M22" s="10">
+        <v>1</v>
+      </c>
+      <c r="N22" s="10">
+        <v>0.1154</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>6</v>
+      </c>
+      <c r="R22" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12520"/>
+    <workbookView windowWidth="29400" windowHeight="12520" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="校边店海报1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="36">
   <si>
     <t>日期</t>
   </si>
@@ -1384,7 +1384,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:19">
@@ -2596,6 +2596,61 @@
       </c>
       <c r="R22" s="3"/>
       <c r="S22" s="9"/>
+    </row>
+    <row r="23" customFormat="1" ht="28" spans="1:19">
+      <c r="A23" s="9">
+        <v>1010</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="3">
+        <v>116</v>
+      </c>
+      <c r="E23" s="3">
+        <v>31</v>
+      </c>
+      <c r="F23" s="3">
+        <v>18</v>
+      </c>
+      <c r="G23" s="3">
+        <v>7</v>
+      </c>
+      <c r="H23" s="3">
+        <v>5</v>
+      </c>
+      <c r="I23" s="3">
+        <v>10</v>
+      </c>
+      <c r="J23" s="3">
+        <v>10</v>
+      </c>
+      <c r="K23" s="10">
+        <v>0.1552</v>
+      </c>
+      <c r="L23" s="10">
+        <v>0.5556</v>
+      </c>
+      <c r="M23" s="10">
+        <v>1</v>
+      </c>
+      <c r="N23" s="10">
+        <v>0.0862</v>
+      </c>
+      <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>10</v>
+      </c>
+      <c r="R23" s="3"/>
+      <c r="S23" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2606,7 +2661,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -3796,6 +3851,60 @@
         <v>3</v>
       </c>
       <c r="R22" s="3"/>
+    </row>
+    <row r="23" customFormat="1" ht="28" spans="1:18">
+      <c r="A23" s="9">
+        <v>1010</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="3">
+        <v>17</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3">
+        <v>2</v>
+      </c>
+      <c r="G23" s="3">
+        <v>2</v>
+      </c>
+      <c r="H23" s="3">
+        <v>2</v>
+      </c>
+      <c r="I23" s="3">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3">
+        <v>3</v>
+      </c>
+      <c r="K23" s="10">
+        <v>0.1176</v>
+      </c>
+      <c r="L23" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="M23" s="3">
+        <v>1</v>
+      </c>
+      <c r="N23" s="10">
+        <v>0.1765</v>
+      </c>
+      <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3806,7 +3915,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -4996,6 +5105,60 @@
         <v>0</v>
       </c>
       <c r="R22" s="3"/>
+    </row>
+    <row r="23" customFormat="1" ht="28" spans="1:18">
+      <c r="A23" s="9">
+        <v>1010</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="3">
+        <v>9</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="10">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N23" s="10">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5006,7 +5169,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -6196,6 +6359,60 @@
         <v>6</v>
       </c>
       <c r="R22" s="3"/>
+    </row>
+    <row r="23" customFormat="1" ht="28" spans="1:18">
+      <c r="A23" s="11">
+        <v>1010</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="3">
+        <v>53</v>
+      </c>
+      <c r="E23" s="3">
+        <v>14</v>
+      </c>
+      <c r="F23" s="3">
+        <v>6</v>
+      </c>
+      <c r="G23" s="3">
+        <v>4</v>
+      </c>
+      <c r="H23" s="3">
+        <v>4</v>
+      </c>
+      <c r="I23" s="3">
+        <v>6</v>
+      </c>
+      <c r="J23" s="3">
+        <v>6</v>
+      </c>
+      <c r="K23" s="10">
+        <v>0.1132</v>
+      </c>
+      <c r="L23" s="10">
+        <v>1</v>
+      </c>
+      <c r="M23" s="10">
+        <v>1</v>
+      </c>
+      <c r="N23" s="10">
+        <v>0.1132</v>
+      </c>
+      <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>6</v>
+      </c>
+      <c r="R23" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12520" activeTab="3"/>
+    <workbookView windowWidth="29400" windowHeight="12520" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="校边店海报1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="36">
   <si>
     <t>日期</t>
   </si>
@@ -1384,7 +1384,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:19">
@@ -2651,6 +2651,61 @@
       </c>
       <c r="R23" s="3"/>
       <c r="S23" s="9"/>
+    </row>
+    <row r="24" customFormat="1" ht="28" spans="1:19">
+      <c r="A24" s="9">
+        <v>1014</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="3">
+        <v>139</v>
+      </c>
+      <c r="E24" s="3">
+        <v>34</v>
+      </c>
+      <c r="F24" s="3">
+        <v>21</v>
+      </c>
+      <c r="G24" s="3">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3">
+        <v>6</v>
+      </c>
+      <c r="I24" s="3">
+        <v>11</v>
+      </c>
+      <c r="J24" s="3">
+        <v>11</v>
+      </c>
+      <c r="K24" s="10">
+        <v>0.1511</v>
+      </c>
+      <c r="L24" s="10">
+        <v>0.5238</v>
+      </c>
+      <c r="M24" s="10">
+        <v>1</v>
+      </c>
+      <c r="N24" s="10">
+        <v>0.0791</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>11</v>
+      </c>
+      <c r="R24" s="3"/>
+      <c r="S24" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2661,7 +2716,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -3905,6 +3960,60 @@
         <v>3</v>
       </c>
       <c r="R23" s="3"/>
+    </row>
+    <row r="24" customFormat="1" ht="28" spans="1:18">
+      <c r="A24" s="9">
+        <v>1014</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="3">
+        <v>20</v>
+      </c>
+      <c r="E24" s="3">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3">
+        <v>4</v>
+      </c>
+      <c r="K24" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="L24" s="3">
+        <v>1.3333</v>
+      </c>
+      <c r="M24" s="3">
+        <v>1</v>
+      </c>
+      <c r="N24" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>4</v>
+      </c>
+      <c r="R24" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3915,7 +4024,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -5159,6 +5268,60 @@
         <v>0</v>
       </c>
       <c r="R23" s="3"/>
+    </row>
+    <row r="24" customFormat="1" ht="28" spans="1:18">
+      <c r="A24" s="9">
+        <v>1014</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="3">
+        <v>18</v>
+      </c>
+      <c r="E24" s="3">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="10">
+        <v>0.0556</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N24" s="10">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5169,7 +5332,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -6413,6 +6576,60 @@
         <v>6</v>
       </c>
       <c r="R23" s="3"/>
+    </row>
+    <row r="24" customFormat="1" ht="28" spans="1:18">
+      <c r="A24" s="11">
+        <v>1014</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="3">
+        <v>57</v>
+      </c>
+      <c r="E24" s="3">
+        <v>15</v>
+      </c>
+      <c r="F24" s="3">
+        <v>7</v>
+      </c>
+      <c r="G24" s="3">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3">
+        <v>7</v>
+      </c>
+      <c r="J24" s="3">
+        <v>7</v>
+      </c>
+      <c r="K24" s="10">
+        <v>0.1228</v>
+      </c>
+      <c r="L24" s="10">
+        <v>1</v>
+      </c>
+      <c r="M24" s="10">
+        <v>1</v>
+      </c>
+      <c r="N24" s="10">
+        <v>0.1228</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>7</v>
+      </c>
+      <c r="R24" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6423,7 +6640,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="10.7692307692308"/>
@@ -6919,6 +7136,41 @@
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
       <c r="Q14" s="5"/>
+    </row>
+    <row r="15" ht="28" spans="1:17">
+      <c r="A15" s="3">
+        <v>947140087</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="4">
+        <v>46306.66875</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6935,6 +7187,7 @@
     <hyperlink ref="E12" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
     <hyperlink ref="E13" r:id="rId2" display="3103935-5宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103935"/>
     <hyperlink ref="E14" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
+    <hyperlink ref="E15" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="36">
   <si>
     <t>日期</t>
   </si>
@@ -1384,7 +1384,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:19">
@@ -2706,6 +2706,61 @@
       </c>
       <c r="R24" s="3"/>
       <c r="S24" s="9"/>
+    </row>
+    <row r="25" customFormat="1" ht="28" spans="1:19">
+      <c r="A25" s="9">
+        <v>1019</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="3">
+        <v>174</v>
+      </c>
+      <c r="E25" s="3">
+        <v>42</v>
+      </c>
+      <c r="F25" s="3">
+        <v>24</v>
+      </c>
+      <c r="G25" s="3">
+        <v>9</v>
+      </c>
+      <c r="H25" s="3">
+        <v>7</v>
+      </c>
+      <c r="I25" s="3">
+        <v>16</v>
+      </c>
+      <c r="J25" s="3">
+        <v>16</v>
+      </c>
+      <c r="K25" s="10">
+        <v>0.1379</v>
+      </c>
+      <c r="L25" s="10">
+        <v>0.6667</v>
+      </c>
+      <c r="M25" s="10">
+        <v>1</v>
+      </c>
+      <c r="N25" s="10">
+        <v>0.092</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>16</v>
+      </c>
+      <c r="R25" s="3"/>
+      <c r="S25" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2716,7 +2771,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -4014,6 +4069,60 @@
         <v>4</v>
       </c>
       <c r="R24" s="3"/>
+    </row>
+    <row r="25" customFormat="1" ht="28" spans="1:18">
+      <c r="A25" s="9">
+        <v>1019</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="3">
+        <v>25</v>
+      </c>
+      <c r="E25" s="3">
+        <v>4</v>
+      </c>
+      <c r="F25" s="3">
+        <v>3</v>
+      </c>
+      <c r="G25" s="3">
+        <v>3</v>
+      </c>
+      <c r="H25" s="3">
+        <v>3</v>
+      </c>
+      <c r="I25" s="3">
+        <v>4</v>
+      </c>
+      <c r="J25" s="3">
+        <v>4</v>
+      </c>
+      <c r="K25" s="10">
+        <v>0.12</v>
+      </c>
+      <c r="L25" s="3">
+        <v>1.3333</v>
+      </c>
+      <c r="M25" s="3">
+        <v>1</v>
+      </c>
+      <c r="N25" s="10">
+        <v>0.16</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>4</v>
+      </c>
+      <c r="R25" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4024,7 +4133,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -5322,6 +5431,60 @@
         <v>0</v>
       </c>
       <c r="R24" s="3"/>
+    </row>
+    <row r="25" customFormat="1" ht="28" spans="1:18">
+      <c r="A25" s="9">
+        <v>1019</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="3">
+        <v>27</v>
+      </c>
+      <c r="E25" s="3">
+        <v>4</v>
+      </c>
+      <c r="F25" s="3">
+        <v>2</v>
+      </c>
+      <c r="G25" s="3">
+        <v>1</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1</v>
+      </c>
+      <c r="I25" s="3">
+        <v>1</v>
+      </c>
+      <c r="J25" s="3">
+        <v>1</v>
+      </c>
+      <c r="K25" s="10">
+        <v>0.0741</v>
+      </c>
+      <c r="L25" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="M25" s="3">
+        <v>1</v>
+      </c>
+      <c r="N25" s="10">
+        <v>0.037</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>1</v>
+      </c>
+      <c r="R25" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5332,7 +5495,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -6630,6 +6793,60 @@
         <v>7</v>
       </c>
       <c r="R24" s="3"/>
+    </row>
+    <row r="25" customFormat="1" ht="28" spans="1:18">
+      <c r="A25" s="11">
+        <v>1019</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="3">
+        <v>61</v>
+      </c>
+      <c r="E25" s="3">
+        <v>15</v>
+      </c>
+      <c r="F25" s="3">
+        <v>7</v>
+      </c>
+      <c r="G25" s="3">
+        <v>5</v>
+      </c>
+      <c r="H25" s="3">
+        <v>5</v>
+      </c>
+      <c r="I25" s="3">
+        <v>7</v>
+      </c>
+      <c r="J25" s="3">
+        <v>7</v>
+      </c>
+      <c r="K25" s="10">
+        <v>0.1148</v>
+      </c>
+      <c r="L25" s="10">
+        <v>1</v>
+      </c>
+      <c r="M25" s="10">
+        <v>1</v>
+      </c>
+      <c r="N25" s="10">
+        <v>0.1148</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>7</v>
+      </c>
+      <c r="R25" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6640,7 +6857,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="10.7692307692308"/>
@@ -7171,6 +7388,111 @@
       <c r="O15" s="5"/>
       <c r="P15" s="5"/>
       <c r="Q15" s="5"/>
+    </row>
+    <row r="16" ht="28" spans="1:17">
+      <c r="A16" s="3">
+        <v>312871432</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="4">
+        <v>46313.4472222222</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+    </row>
+    <row r="17" ht="28" spans="1:17">
+      <c r="A17" s="3">
+        <v>428548852</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="4">
+        <v>46312.4236111111</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+    </row>
+    <row r="18" ht="28" spans="1:17">
+      <c r="A18" s="3">
+        <v>816436940</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="4">
+        <v>46311.8666666667</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -7188,6 +7510,9 @@
     <hyperlink ref="E13" r:id="rId2" display="3103935-5宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103935"/>
     <hyperlink ref="E14" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
     <hyperlink ref="E15" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
+    <hyperlink ref="E16" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
+    <hyperlink ref="E17" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
+    <hyperlink ref="E18" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/AI大阅读抽奖数据.xlsx
+++ b/AI大阅读抽奖数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12520" activeTab="4"/>
+    <workbookView windowWidth="29400" windowHeight="12520"/>
   </bookViews>
   <sheets>
     <sheet name="校边店海报1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="36">
   <si>
     <t>日期</t>
   </si>
@@ -1384,7 +1384,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S25"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:19">
@@ -2761,6 +2761,116 @@
       </c>
       <c r="R25" s="3"/>
       <c r="S25" s="9"/>
+    </row>
+    <row r="26" customFormat="1" ht="28" spans="1:19">
+      <c r="A26" s="9">
+        <v>1023</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="3">
+        <v>203</v>
+      </c>
+      <c r="E26" s="3">
+        <v>43</v>
+      </c>
+      <c r="F26" s="3">
+        <v>24</v>
+      </c>
+      <c r="G26" s="3">
+        <v>9</v>
+      </c>
+      <c r="H26" s="3">
+        <v>7</v>
+      </c>
+      <c r="I26" s="3">
+        <v>17</v>
+      </c>
+      <c r="J26" s="3">
+        <v>17</v>
+      </c>
+      <c r="K26" s="10">
+        <v>0.1182</v>
+      </c>
+      <c r="L26" s="10">
+        <v>0.7083</v>
+      </c>
+      <c r="M26" s="10">
+        <v>1</v>
+      </c>
+      <c r="N26" s="10">
+        <v>0.0837</v>
+      </c>
+      <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>17</v>
+      </c>
+      <c r="R26" s="3"/>
+      <c r="S26" s="9"/>
+    </row>
+    <row r="27" customFormat="1" ht="28" spans="1:19">
+      <c r="A27" s="9">
+        <v>1028</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="3">
+        <v>233</v>
+      </c>
+      <c r="E27" s="3">
+        <v>45</v>
+      </c>
+      <c r="F27" s="3">
+        <v>26</v>
+      </c>
+      <c r="G27" s="3">
+        <v>10</v>
+      </c>
+      <c r="H27" s="3">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3">
+        <v>18</v>
+      </c>
+      <c r="J27" s="3">
+        <v>18</v>
+      </c>
+      <c r="K27" s="10">
+        <v>0.1116</v>
+      </c>
+      <c r="L27" s="10">
+        <v>0.6923</v>
+      </c>
+      <c r="M27" s="10">
+        <v>1</v>
+      </c>
+      <c r="N27" s="10">
+        <v>0.0773</v>
+      </c>
+      <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>18</v>
+      </c>
+      <c r="R27" s="3"/>
+      <c r="S27" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2771,7 +2881,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -4123,6 +4233,114 @@
         <v>4</v>
       </c>
       <c r="R25" s="3"/>
+    </row>
+    <row r="26" customFormat="1" ht="28" spans="1:18">
+      <c r="A26" s="9">
+        <v>1023</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="3">
+        <v>33</v>
+      </c>
+      <c r="E26" s="3">
+        <v>4</v>
+      </c>
+      <c r="F26" s="3">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3">
+        <v>3</v>
+      </c>
+      <c r="H26" s="3">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3">
+        <v>4</v>
+      </c>
+      <c r="J26" s="3">
+        <v>4</v>
+      </c>
+      <c r="K26" s="10">
+        <v>0.0909</v>
+      </c>
+      <c r="L26" s="3">
+        <v>1.3333</v>
+      </c>
+      <c r="M26" s="3">
+        <v>1</v>
+      </c>
+      <c r="N26" s="10">
+        <v>0.1212</v>
+      </c>
+      <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" customFormat="1" ht="28" spans="1:18">
+      <c r="A27" s="9">
+        <v>1028</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="3">
+        <v>49</v>
+      </c>
+      <c r="E27" s="3">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3">
+        <v>3</v>
+      </c>
+      <c r="H27" s="3">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3">
+        <v>5</v>
+      </c>
+      <c r="J27" s="3">
+        <v>5</v>
+      </c>
+      <c r="K27" s="10">
+        <v>0.0612</v>
+      </c>
+      <c r="L27" s="3">
+        <v>1.6667</v>
+      </c>
+      <c r="M27" s="3">
+        <v>1</v>
+      </c>
+      <c r="N27" s="10">
+        <v>0.102</v>
+      </c>
+      <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4133,7 +4351,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -5485,6 +5703,114 @@
         <v>1</v>
       </c>
       <c r="R25" s="3"/>
+    </row>
+    <row r="26" customFormat="1" ht="28" spans="1:18">
+      <c r="A26" s="9">
+        <v>1023</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="3">
+        <v>33</v>
+      </c>
+      <c r="E26" s="3">
+        <v>4</v>
+      </c>
+      <c r="F26" s="3">
+        <v>2</v>
+      </c>
+      <c r="G26" s="3">
+        <v>1</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1</v>
+      </c>
+      <c r="J26" s="3">
+        <v>1</v>
+      </c>
+      <c r="K26" s="10">
+        <v>0.0606</v>
+      </c>
+      <c r="L26" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="M26" s="3">
+        <v>1</v>
+      </c>
+      <c r="N26" s="10">
+        <v>0.0303</v>
+      </c>
+      <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>1</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" customFormat="1" ht="28" spans="1:18">
+      <c r="A27" s="9">
+        <v>1028</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="3">
+        <v>37</v>
+      </c>
+      <c r="E27" s="3">
+        <v>4</v>
+      </c>
+      <c r="F27" s="3">
+        <v>2</v>
+      </c>
+      <c r="G27" s="3">
+        <v>1</v>
+      </c>
+      <c r="H27" s="3">
+        <v>1</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1</v>
+      </c>
+      <c r="J27" s="3">
+        <v>1</v>
+      </c>
+      <c r="K27" s="10">
+        <v>0.0541</v>
+      </c>
+      <c r="L27" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="M27" s="3">
+        <v>1</v>
+      </c>
+      <c r="N27" s="10">
+        <v>0.027</v>
+      </c>
+      <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>1</v>
+      </c>
+      <c r="R27" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5495,7 +5821,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" ht="28" spans="1:18">
@@ -6847,6 +7173,114 @@
         <v>7</v>
       </c>
       <c r="R25" s="3"/>
+    </row>
+    <row r="26" customFormat="1" ht="28" spans="1:18">
+      <c r="A26" s="11">
+        <v>1023</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="3">
+        <v>64</v>
+      </c>
+      <c r="E26" s="3">
+        <v>15</v>
+      </c>
+      <c r="F26" s="3">
+        <v>7</v>
+      </c>
+      <c r="G26" s="3">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3">
+        <v>5</v>
+      </c>
+      <c r="I26" s="3">
+        <v>7</v>
+      </c>
+      <c r="J26" s="3">
+        <v>7</v>
+      </c>
+      <c r="K26" s="10">
+        <v>0.1094</v>
+      </c>
+      <c r="L26" s="10">
+        <v>1</v>
+      </c>
+      <c r="M26" s="10">
+        <v>1</v>
+      </c>
+      <c r="N26" s="10">
+        <v>0.1094</v>
+      </c>
+      <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>7</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" customFormat="1" ht="28" spans="1:18">
+      <c r="A27" s="11">
+        <v>1028</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="3">
+        <v>67</v>
+      </c>
+      <c r="E27" s="3">
+        <v>15</v>
+      </c>
+      <c r="F27" s="3">
+        <v>7</v>
+      </c>
+      <c r="G27" s="3">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3">
+        <v>5</v>
+      </c>
+      <c r="I27" s="3">
+        <v>7</v>
+      </c>
+      <c r="J27" s="3">
+        <v>7</v>
+      </c>
+      <c r="K27" s="10">
+        <v>0.1045</v>
+      </c>
+      <c r="L27" s="10">
+        <v>1</v>
+      </c>
+      <c r="M27" s="10">
+        <v>1</v>
+      </c>
+      <c r="N27" s="10">
+        <v>0.1045</v>
+      </c>
+      <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>7</v>
+      </c>
+      <c r="R27" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6857,7 +7291,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="10.7692307692308"/>
@@ -7493,6 +7927,41 @@
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
       <c r="Q18" s="5"/>
+    </row>
+    <row r="19" ht="28" spans="1:17">
+      <c r="A19" s="3">
+        <v>165195196</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="4">
+        <v>46321.6263888889</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -7513,6 +7982,7 @@
     <hyperlink ref="E16" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
     <hyperlink ref="E17" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
     <hyperlink ref="E18" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
+    <hyperlink ref="E19" r:id="rId1" display="3103936-1宝石" tooltip="https://eagle.zhenguanyu.com/new/gem-mall/invite-fresh-gifts/3103936"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
